--- a/Numerical methods/LW11/LW11.xlsx
+++ b/Numerical methods/LW11/LW11.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr codeName="ЭтаКнига"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\studies\Numerical methods\LW11\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\studies\Numerical methods\LW11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EC3BCB-009B-42BE-AADA-8D5D560F7541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E298BF-929D-4F82-9F55-93BAF3714727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Метод Эйлера" sheetId="1" r:id="rId1"/>
@@ -31,9 +31,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -880,6 +877,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -887,7 +885,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1630,6 +1627,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1637,7 +1635,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2380,6 +2377,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2387,7 +2385,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4209,6 +4206,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4216,7 +4214,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6921,13 +6918,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Лист1"/>
   <dimension ref="B1:E85"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>2</v>
       </c>
@@ -6941,7 +6939,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -6955,7 +6953,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -6969,7 +6967,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>0</v>
       </c>
@@ -6985,7 +6983,7 @@
         <v>0.1585290151921035</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>1</v>
       </c>
@@ -7002,7 +7000,7 @@
         <v>0.23199941387832146</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7">
         <v>2</v>
       </c>
@@ -7019,7 +7017,7 @@
         <v>0.30468537259954775</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>3</v>
       </c>
@@ -7036,7 +7034,7 @@
         <v>0.37623658748695432</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9">
         <v>4</v>
       </c>
@@ -7053,7 +7051,7 @@
         <v>0.44636659149604563</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>5</v>
       </c>
@@ -7070,7 +7068,7 @@
         <v>0.51484801748990161</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>6</v>
       </c>
@@ -7087,7 +7085,7 @@
         <v>0.58150697021338038</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12">
         <v>7</v>
       </c>
@@ -7104,7 +7102,7 @@
         <v>0.64621700519592096</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13">
         <v>8</v>
       </c>
@@ -7121,7 +7119,7 @@
         <v>0.70889309355118668</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14">
         <v>9</v>
       </c>
@@ -7138,7 +7136,7 @@
         <v>0.76948584199902748</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15">
         <v>10</v>
       </c>
@@ -7155,7 +7153,7 @@
         <v>0.82797614372569073</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16">
         <v>11</v>
       </c>
@@ -7172,7 +7170,7 @@
         <v>0.88437036036529626</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17">
         <v>12</v>
       </c>
@@ -7189,7 +7187,7 @@
         <v>0.93869607813910672</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18">
         <v>13</v>
       </c>
@@ -7206,7 +7204,7 @@
         <v>0.99099844013828686</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19">
         <v>14</v>
       </c>
@@ -7223,7 +7221,7 @@
         <v>1.0413370292430688</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B20">
         <v>15</v>
       </c>
@@ -7240,7 +7238,7 @@
         <v>1.0897832594302241</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B21">
         <v>16</v>
       </c>
@@ -7257,7 +7255,7 @@
         <v>1.1364182246044363</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B22">
         <v>17</v>
       </c>
@@ -7274,7 +7272,7 @@
         <v>1.1813309513267405</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23">
         <v>18</v>
       </c>
@@ -7291,7 +7289,7 @@
         <v>1.2246170030521912</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24">
         <v>19</v>
       </c>
@@ -7308,7 +7306,7 @@
         <v>1.2663773872870281</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B25">
         <v>20</v>
       </c>
@@ -7325,7 +7323,7 @@
         <v>1.3067177223562334</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B26">
         <v>21</v>
       </c>
@@ -7342,7 +7340,7 @@
         <v>1.3457476264643464</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B27">
         <v>22</v>
       </c>
@@ -7359,7 +7357,7 @@
         <v>1.3835802979085434</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B28">
         <v>23</v>
       </c>
@@ -7376,7 +7374,7 @@
         <v>1.4203322613236651</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B29">
         <v>24</v>
       </c>
@@ -7393,7 +7391,7 @@
         <v>1.4561232605041856</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B30">
         <v>25</v>
       </c>
@@ -7410,7 +7408,7 @@
         <v>1.4910762835590623</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B31">
         <v>26</v>
       </c>
@@ -7427,7 +7425,7 @@
         <v>1.5253177108836717</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B32">
         <v>27</v>
       </c>
@@ -7444,7 +7442,7 @@
         <v>1.5589775806980475</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B33">
         <v>28</v>
       </c>
@@ -7461,7 +7459,7 @@
         <v>1.5921899707521727</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B34">
         <v>29</v>
       </c>
@@ -7478,7 +7476,7 @@
         <v>1.6250934983046523</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B35">
         <v>30</v>
       </c>
@@ -7495,7 +7493,7 @@
         <v>1.6578319437162459</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B36">
         <v>31</v>
       </c>
@@ -7512,7 +7510,7 @@
         <v>1.6905550060403836</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B37">
         <v>32</v>
       </c>
@@ -7529,7 +7527,7 @@
         <v>1.7234192019084962</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B38">
         <v>33</v>
       </c>
@@ -7546,7 +7544,7 @@
         <v>1.7565889218553874</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B39">
         <v>34</v>
       </c>
@@ -7563,7 +7561,7 @@
         <v>1.7902376610443544</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B40">
         <v>35</v>
       </c>
@@ -7580,7 +7578,7 @@
         <v>1.8245494441372265</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B41">
         <v>36</v>
       </c>
@@ -7597,7 +7595,7 @@
         <v>1.8597204667681768</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B42">
         <v>37</v>
       </c>
@@ -7614,7 +7612,7 @@
         <v>1.895960978611078</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B43">
         <v>38</v>
       </c>
@@ -7631,7 +7629,7 @@
         <v>1.9334974351673013</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B44">
         <v>39</v>
       </c>
@@ -7648,7 +7646,7 @@
         <v>1.9725749467863958</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B45">
         <v>40</v>
       </c>
@@ -7665,7 +7663,7 @@
         <v>2.0134600534934259</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B46">
         <v>41</v>
       </c>
@@ -7682,7 +7680,7 @@
         <v>2.0564438520470216</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B47">
         <v>42</v>
       </c>
@@ -7699,7 +7697,7 @@
         <v>2.1018454959472939</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B48">
         <v>43</v>
       </c>
@@ -7716,7 +7714,7 @@
         <v>2.1500160778457276</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B49">
         <v>44</v>
       </c>
@@ -7733,7 +7731,7 @@
         <v>2.2013428840189917</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B50">
         <v>45</v>
       </c>
@@ -7750,7 +7748,7 @@
         <v>2.2562539779322641</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B51">
         <v>46</v>
       </c>
@@ -7767,7 +7765,7 @@
         <v>2.3152230181885698</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B52">
         <v>47</v>
       </c>
@@ -7784,7 +7782,7 @@
         <v>2.3787741364153097</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B53">
         <v>48</v>
       </c>
@@ -7801,7 +7799,7 @@
         <v>2.4474865803033077</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B54">
         <v>49</v>
       </c>
@@ -7818,7 +7816,7 @@
         <v>2.5219986486768979</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B55">
         <v>50</v>
       </c>
@@ -7835,7 +7833,7 @@
         <v>2.6030101855976504</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B56">
         <v>51</v>
       </c>
@@ -7852,7 +7850,7 @@
         <v>2.6912825283386979</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B57">
         <v>52</v>
       </c>
@@ -7869,7 +7867,7 @@
         <v>2.7876342815026645</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B58">
         <v>53</v>
       </c>
@@ -7886,7 +7884,7 @@
         <v>2.8929305734344646</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B59">
         <v>54</v>
       </c>
@@ -7903,7 +7901,7 @@
         <v>3.0080625008385384</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B60">
         <v>55</v>
       </c>
@@ -7920,7 +7918,7 @@
         <v>3.1339122632890186</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B61">
         <v>56</v>
       </c>
@@ -7937,7 +7935,7 @@
         <v>3.2712980688766109</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B62">
         <v>57</v>
       </c>
@@ -7954,7 +7952,7 @@
         <v>3.4208914187854331</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B63">
         <v>58</v>
       </c>
@@ -7971,7 +7969,7 @@
         <v>3.5830982538339651</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B64">
         <v>59</v>
       </c>
@@ -7988,7 +7986,7 @@
         <v>3.7578954766959951</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B65">
         <v>60</v>
       </c>
@@ -8005,7 +8003,7 @@
         <v>3.9446169621796363</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B66">
         <v>61</v>
       </c>
@@ -8022,7 +8020,7 @@
         <v>4.1416904941777783</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B67">
         <v>62</v>
       </c>
@@ -8039,7 +8037,7 @@
         <v>4.3463418666664317</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B68">
         <v>63</v>
       </c>
@@ -8056,7 +8054,7 @@
         <v>4.5543070566720498</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B69">
         <v>64</v>
       </c>
@@ -8073,7 +8071,7 @@
         <v>4.7596276432985203</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B70">
         <v>65</v>
       </c>
@@ -8090,7 +8088,7 @@
         <v>4.9546415232799976</v>
       </c>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B71">
         <v>66</v>
       </c>
@@ -8107,7 +8105,7 @@
         <v>5.1303022991989522</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B72">
         <v>67</v>
       </c>
@@ -8124,7 +8122,7 @@
         <v>5.2769368293062922</v>
       </c>
     </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B73">
         <v>68</v>
       </c>
@@ -8141,7 +8139,7 @@
         <v>5.3854517430462883</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B74">
         <v>69</v>
       </c>
@@ -8158,7 +8156,7 @@
         <v>5.4488246821584569</v>
       </c>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B75">
         <v>70</v>
       </c>
@@ -8175,7 +8173,7 @@
         <v>5.463522596370697</v>
       </c>
     </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B76">
         <v>71</v>
       </c>
@@ -8192,7 +8190,7 @@
         <v>5.4303932884872417</v>
       </c>
     </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B77">
         <v>72</v>
       </c>
@@ -8209,7 +8207,7 @@
         <v>5.3546832456657745</v>
       </c>
     </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B78">
         <v>73</v>
       </c>
@@ -8226,7 +8224,7 @@
         <v>5.2451377360947209</v>
       </c>
     </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B79">
         <v>74</v>
       </c>
@@ -8243,7 +8241,7 @@
         <v>5.1124848939298939</v>
       </c>
     </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B80">
         <v>75</v>
       </c>
@@ -8260,7 +8258,7 @@
         <v>4.967796205605203</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B81">
         <v>76</v>
       </c>
@@ -8277,7 +8275,7 @@
         <v>4.8211645094315578</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B82">
         <v>77</v>
       </c>
@@ -8294,7 +8292,7 @@
         <v>4.6809239613652167</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B83">
         <v>78</v>
       </c>
@@ -8311,7 +8309,7 @@
         <v>4.5534052981177986</v>
       </c>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B84">
         <v>79</v>
       </c>
@@ -8328,7 +8326,7 @@
         <v>4.4430794031728995</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B85">
         <v>80</v>
       </c>
@@ -8357,18 +8355,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71AEA1B1-C909-4111-92DC-3F2D337C3F72}">
+  <sheetPr codeName="Лист2"/>
   <dimension ref="B1:Q85"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="5.42578125" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="5.453125" customWidth="1"/>
+    <col min="6" max="6" width="9.1796875" customWidth="1"/>
+    <col min="7" max="7" width="9.54296875" customWidth="1"/>
+    <col min="9" max="9" width="17.7265625" customWidth="1"/>
+    <col min="12" max="12" width="18.26953125" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:17" x14ac:dyDescent="0.35">
       <c r="I1" t="s">
         <v>2</v>
       </c>
@@ -8382,7 +8381,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.35">
       <c r="I2" t="s">
         <v>0</v>
       </c>
@@ -8396,7 +8395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -8446,7 +8445,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>0</v>
       </c>
@@ -8511,12 +8510,12 @@
         <v>1.154820699103269E-2</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <f>C5 + $K$2</f>
+        <f t="shared" ref="C6:C37" si="0">C5 + $K$2</f>
         <v>1.05</v>
       </c>
       <c r="D6">
@@ -8576,5138 +8575,5138 @@
         <v>1.5127104817839177E-2</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7">
-        <f>C6 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="D7">
-        <f t="shared" ref="D7:D70" si="0">D6 + (F6 + 2*J6 + 2*M6 + Q6)/6</f>
+        <f t="shared" ref="D7:D70" si="1">D6 + (F6 + 2*J6 + 2*M6 + Q6)/6</f>
         <v>2.0230815530554382</v>
       </c>
       <c r="E7">
-        <f t="shared" ref="E7:E70" si="1">SIN(C7 - D7) + C7</f>
+        <f t="shared" ref="E7:E70" si="2">SIN(C7 - D7) + C7</f>
         <v>0.30253529346476427</v>
       </c>
       <c r="F7">
-        <f t="shared" ref="F7:F70" si="2">$K$2 * E7</f>
+        <f t="shared" ref="F7:F70" si="3">$K$2 * E7</f>
         <v>1.5126764673238214E-2</v>
       </c>
       <c r="G7">
-        <f t="shared" ref="G7:G70" si="3">C7 + $K$2 / 2</f>
+        <f t="shared" ref="G7:G70" si="4">C7 + $K$2 / 2</f>
         <v>1.125</v>
       </c>
       <c r="H7">
-        <f t="shared" ref="H7:H70" si="4">D7 + F7 / 2</f>
+        <f t="shared" ref="H7:H70" si="5">D7 + F7 / 2</f>
         <v>2.0306449353920573</v>
       </c>
       <c r="I7">
-        <f t="shared" ref="I7:I70" si="5">SIN(G7 - H7) + G7</f>
+        <f t="shared" ref="I7:I70" si="6">SIN(G7 - H7) + G7</f>
         <v>0.33817664133676628</v>
       </c>
       <c r="J7">
-        <f t="shared" ref="J7:J70" si="6">$K$2 * I7</f>
+        <f t="shared" ref="J7:J70" si="7">$K$2 * I7</f>
         <v>1.6908832066838315E-2</v>
       </c>
       <c r="K7">
-        <f t="shared" ref="K7:K70" si="7">D7 + J7/2</f>
+        <f t="shared" ref="K7:K70" si="8">D7 + J7/2</f>
         <v>2.0315359690888575</v>
       </c>
       <c r="L7">
-        <f t="shared" ref="L7:L70" si="8">SIN(G7 - K7) + G7</f>
+        <f t="shared" ref="L7:L70" si="9">SIN(G7 - K7) + G7</f>
         <v>0.33762702713030246</v>
       </c>
       <c r="M7">
-        <f t="shared" ref="M7:M70" si="9" xml:space="preserve"> $K$2 * L7</f>
+        <f t="shared" ref="M7:M70" si="10" xml:space="preserve"> $K$2 * L7</f>
         <v>1.6881351356515122E-2</v>
       </c>
       <c r="N7">
-        <f t="shared" ref="N7:N70" si="10">C7 + $K$2</f>
+        <f t="shared" ref="N7:N70" si="11">C7 + $K$2</f>
         <v>1.1500000000000001</v>
       </c>
       <c r="O7">
-        <f t="shared" ref="O7:O70" si="11">D7 + M7</f>
+        <f t="shared" ref="O7:O70" si="12">D7 + M7</f>
         <v>2.0399629044119534</v>
       </c>
       <c r="P7">
-        <f t="shared" ref="P7:P70" si="12">SIN(N7 - O7) + N7</f>
+        <f t="shared" ref="P7:P70" si="13">SIN(N7 - O7) + N7</f>
         <v>0.37295160141707784</v>
       </c>
       <c r="Q7">
-        <f t="shared" ref="Q7:Q70" si="13">$K$2 * P7</f>
+        <f t="shared" ref="Q7:Q70" si="14">$K$2 * P7</f>
         <v>1.8647580070853893E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8">
-        <f>C7 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>1.1500000000000001</v>
       </c>
       <c r="D8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.0399740049872381</v>
       </c>
       <c r="E8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.3729446143093873</v>
       </c>
       <c r="F8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.8647230715469365E-2</v>
       </c>
       <c r="G8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.175</v>
       </c>
       <c r="H8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.0492976203449729</v>
       </c>
       <c r="I8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.40790691020793024</v>
       </c>
       <c r="J8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.0395345510396512E-2</v>
       </c>
       <c r="K8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.0501716777424366</v>
       </c>
       <c r="L8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.40734646418199483</v>
       </c>
       <c r="M8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.0367323209099744E-2</v>
       </c>
       <c r="N8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="O8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.0603413281963379</v>
       </c>
       <c r="P8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.44193478595101565</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.2096739297550783E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9">
-        <f>C8 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="D9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.060352222895907</v>
       </c>
       <c r="E9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.4419276807043806</v>
       </c>
       <c r="F9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.2096384035219033E-2</v>
       </c>
       <c r="G9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.2250000000000001</v>
       </c>
       <c r="H9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.0714004149135166</v>
       </c>
       <c r="I9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.47610012238836974</v>
       </c>
       <c r="J9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.3805006119418489E-2</v>
       </c>
       <c r="K9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.0722547259556161</v>
       </c>
       <c r="L9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.47553425820573259</v>
       </c>
       <c r="M9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.3776712910286629E-2</v>
       </c>
       <c r="N9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.2500000000000002</v>
       </c>
       <c r="O9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.0841289358061936</v>
       </c>
       <c r="P9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.50928840827600674</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.5464420413800339E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>5</v>
       </c>
       <c r="C10">
-        <f>C9 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>1.2500000000000002</v>
       </c>
       <c r="D10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.084139596647312</v>
       </c>
       <c r="E10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.50928124611829284</v>
       </c>
       <c r="F10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.5464062305914643E-2</v>
       </c>
       <c r="G10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.2750000000000001</v>
       </c>
       <c r="H10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.0968716278002693</v>
       </c>
       <c r="I10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.54257858743920417</v>
       </c>
       <c r="J10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.7128929371960209E-2</v>
       </c>
       <c r="K10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.097704061333292</v>
       </c>
       <c r="L10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.54201207758226955</v>
       </c>
       <c r="M10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.7100603879113477E-2</v>
       </c>
       <c r="N10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.3000000000000003</v>
       </c>
       <c r="O10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.1112402005264252</v>
       </c>
       <c r="P10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.57485826654156935</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.874291332707847E-2</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>6</v>
       </c>
       <c r="C11">
-        <f>C10 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>1.3000000000000003</v>
       </c>
       <c r="D11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.1112506036698355</v>
       </c>
       <c r="E11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.5748511029799851</v>
       </c>
       <c r="F11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.8742555148999257E-2</v>
       </c>
       <c r="G11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.3250000000000002</v>
       </c>
       <c r="H11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.125621881244335</v>
       </c>
       <c r="I11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.60721077900686826</v>
       </c>
       <c r="J11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.0360538950343414E-2</v>
       </c>
       <c r="K11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.1264308731450074</v>
       </c>
       <c r="L11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.60664774487687312</v>
       </c>
       <c r="M11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.0332387243843656E-2</v>
       </c>
       <c r="N11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.3500000000000003</v>
       </c>
       <c r="O11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.1415829909136792</v>
       </c>
       <c r="P11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.63853343733123213</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.1926671866561611E-2</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B12">
         <v>7</v>
       </c>
       <c r="C12">
-        <f>C11 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>1.3500000000000003</v>
       </c>
       <c r="D12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.1415931169038247</v>
       </c>
       <c r="E12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.63852632163240386</v>
       </c>
       <c r="F12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.1926316081620193E-2</v>
       </c>
       <c r="G12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.3750000000000002</v>
       </c>
       <c r="H12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.1575562749446346</v>
       </c>
       <c r="I12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.66990559011681727</v>
       </c>
       <c r="J12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.3495279505840865E-2</v>
       </c>
       <c r="K12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.1583407566567452</v>
       </c>
       <c r="L12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.66934952060868902</v>
       </c>
       <c r="M12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.346747603043445E-2</v>
       </c>
       <c r="N12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.4000000000000004</v>
       </c>
       <c r="O12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.1750605929342592</v>
       </c>
       <c r="P12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.70024063707117867</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.5012031853558938E-2</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B13">
         <v>8</v>
       </c>
       <c r="C13">
-        <f>C12 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>1.4000000000000004</v>
       </c>
       <c r="D13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.1750704267384462</v>
       </c>
       <c r="E13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.70023361204540258</v>
       </c>
       <c r="F13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.5011680602270133E-2</v>
       </c>
       <c r="G13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.4250000000000003</v>
       </c>
       <c r="H13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.1925762670395814</v>
       </c>
       <c r="I13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.73060682813737021</v>
       </c>
       <c r="J13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.6530341406868512E-2</v>
       </c>
       <c r="K13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.1933355974418807</v>
       </c>
       <c r="L13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.73006061740513994</v>
       </c>
       <c r="M13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.6503030870256997E-2</v>
       </c>
       <c r="N13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.4500000000000004</v>
       </c>
       <c r="O13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.2115734576087034</v>
       </c>
       <c r="P13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.75993890942883846</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.7996945471441924E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B14">
         <v>9</v>
       </c>
       <c r="C14">
-        <f>C13 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>1.4500000000000004</v>
       </c>
       <c r="D14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.2115829885097735</v>
       </c>
       <c r="E14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.75993201145980638</v>
       </c>
       <c r="F14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.799660057299032E-2</v>
       </c>
       <c r="G14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.4750000000000003</v>
       </c>
       <c r="H14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.2305812887962686</v>
       </c>
       <c r="I14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.78928811105606733</v>
       </c>
       <c r="J14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.9464405552803367E-2</v>
       </c>
       <c r="K14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.2313151912861753</v>
       </c>
       <c r="L14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.78875410791256384</v>
       </c>
       <c r="M14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.9437705395628193E-2</v>
       </c>
       <c r="N14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.5000000000000004</v>
       </c>
       <c r="O14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.2510206939054016</v>
       </c>
       <c r="P14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.81761476480830242</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.0880738240415125E-2</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B15">
         <v>10</v>
       </c>
       <c r="C15">
-        <f>C14 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>1.5000000000000004</v>
       </c>
       <c r="D15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.2510299152948181</v>
       </c>
       <c r="E15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.8176080240685687</v>
       </c>
       <c r="F15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.0880401203428438E-2</v>
       </c>
       <c r="G15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5250000000000004</v>
       </c>
       <c r="H15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.2714701158965322</v>
       </c>
       <c r="I15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.84594825815292896</v>
       </c>
       <c r="J15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.2297412907646451E-2</v>
       </c>
       <c r="K15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.2721786217486413</v>
       </c>
       <c r="L15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.84542832127946632</v>
       </c>
       <c r="M15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.2271416063973319E-2</v>
       </c>
       <c r="N15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.5500000000000005</v>
       </c>
       <c r="O15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.2933013313587916</v>
       </c>
       <c r="P15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.87327783784726298</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.3663891892363152E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B16">
         <v>11</v>
       </c>
       <c r="C16">
-        <f>C15 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>1.5500000000000005</v>
       </c>
       <c r="D16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.2933102404679899</v>
       </c>
       <c r="E16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.87327127864500953</v>
       </c>
       <c r="F16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.3663563932250481E-2</v>
       </c>
       <c r="G16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5750000000000004</v>
       </c>
       <c r="H16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.3151420224341153</v>
       </c>
       <c r="I16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.90060721607029881</v>
       </c>
       <c r="J16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.5030360803514941E-2</v>
       </c>
       <c r="K16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.3158254208697473</v>
       </c>
       <c r="L16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.90010277078382028</v>
       </c>
       <c r="M16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.5005138539191018E-2</v>
       </c>
       <c r="N16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.6000000000000005</v>
       </c>
       <c r="O16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.3383153790071809</v>
       </c>
       <c r="P16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.92695708421676026</v>
       </c>
       <c r="Q16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.6347854210838015E-2</v>
       </c>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B17">
         <v>12</v>
       </c>
       <c r="C17">
-        <f>C16 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>1.6000000000000005</v>
       </c>
       <c r="D17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.3383239766060733</v>
       </c>
       <c r="E17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.92695072542800594</v>
       </c>
       <c r="F17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.63475362714003E-2</v>
       </c>
       <c r="G17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.6250000000000004</v>
       </c>
       <c r="H17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.3614977447417735</v>
       </c>
       <c r="I17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.95330252381089731</v>
       </c>
       <c r="J17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.7665126190544867E-2</v>
       </c>
       <c r="K17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.3621565397013455</v>
       </c>
       <c r="L17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.95281461746771201</v>
       </c>
       <c r="M17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.7640730873385606E-2</v>
       </c>
       <c r="N17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.6500000000000006</v>
       </c>
       <c r="O17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.385964707479459</v>
       </c>
       <c r="P17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.97869750684127343</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.8934875342063672E-2</v>
       </c>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B18">
         <v>13</v>
       </c>
       <c r="C18">
-        <f>C17 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>1.6500000000000006</v>
       </c>
       <c r="D18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.3859729975629609</v>
       </c>
       <c r="E18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.97869136239133669</v>
       </c>
       <c r="F18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.893456811956684E-2</v>
       </c>
       <c r="G18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.6750000000000005</v>
       </c>
       <c r="H18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.4104402816227442</v>
       </c>
       <c r="I18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.0040862949206972</v>
       </c>
       <c r="J18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5.0204314746034866E-2</v>
       </c>
       <c r="K18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.4110751549359781</v>
       </c>
       <c r="L18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.0036156491048804</v>
       </c>
       <c r="M18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.0180782455244023E-2</v>
       </c>
       <c r="N18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.7000000000000006</v>
       </c>
       <c r="O18">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.4361537800182047</v>
       </c>
       <c r="P18">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.0285573813973854</v>
       </c>
       <c r="Q18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.1427869069869271E-2</v>
       </c>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B19">
         <v>14</v>
       </c>
       <c r="C19">
-        <f>C18 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>1.7000000000000006</v>
       </c>
       <c r="D19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.43616176949496</v>
       </c>
       <c r="E19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0285514607647366</v>
       </c>
       <c r="F19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.1427573038236835E-2</v>
       </c>
       <c r="G19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.7250000000000005</v>
       </c>
       <c r="H19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.4618755560140784</v>
       </c>
       <c r="I19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.0530226795121971</v>
       </c>
       <c r="J19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5.265113397560986E-2</v>
       </c>
       <c r="K19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.4624873364827651</v>
       </c>
       <c r="L19">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.0525697379753454</v>
       </c>
       <c r="M19">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.2628486898767271E-2</v>
       </c>
       <c r="N19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.7500000000000007</v>
       </c>
       <c r="O19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.4887902563937274</v>
       </c>
       <c r="P19">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.0766059391745499</v>
       </c>
       <c r="Q19">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.38302969587275E-2</v>
       </c>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B20">
         <v>15</v>
       </c>
       <c r="C20">
-        <f>C19 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>1.7500000000000007</v>
       </c>
       <c r="D20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.4887979547859129</v>
       </c>
       <c r="E20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0766002478983863</v>
       </c>
       <c r="F20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.3830012394919316E-2</v>
       </c>
       <c r="G20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.7750000000000006</v>
       </c>
       <c r="H20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.5157129609833726</v>
       </c>
       <c r="I20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.1001857605214098</v>
       </c>
       <c r="J20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5.5009288026070496E-2</v>
       </c>
       <c r="K20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.5163025987989482</v>
       </c>
       <c r="L20">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.0997507324397429</v>
       </c>
       <c r="M20">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.4987536621987146E-2</v>
       </c>
       <c r="N20">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.8000000000000007</v>
       </c>
       <c r="O20">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.5437854914078999</v>
       </c>
       <c r="P20">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.1229214599128983</v>
       </c>
       <c r="Q20">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.6146072995644919E-2</v>
       </c>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B21">
         <v>16</v>
       </c>
       <c r="C21">
-        <f>C20 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>1.8000000000000007</v>
       </c>
       <c r="D21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.5437929105670261</v>
       </c>
       <c r="E21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.122916000092482</v>
       </c>
       <c r="F21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6145800004624102E-2</v>
       </c>
       <c r="G21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.8250000000000006</v>
       </c>
       <c r="H21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.5718658105693382</v>
       </c>
       <c r="I21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.1456578356564346</v>
       </c>
       <c r="J21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5.7282891782821733E-2</v>
       </c>
       <c r="K21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.5724343564584369</v>
       </c>
       <c r="L21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.1452407341894824</v>
       </c>
       <c r="M21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.7262036709474121E-2</v>
       </c>
       <c r="N21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.8500000000000008</v>
       </c>
       <c r="O21">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.6010549472765003</v>
       </c>
       <c r="P21">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.1675897262429193</v>
       </c>
       <c r="Q21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.837948631214597E-2</v>
       </c>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B22">
         <v>17</v>
       </c>
       <c r="C22">
-        <f>C21 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>1.8500000000000008</v>
       </c>
       <c r="D22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.601062101117253</v>
       </c>
       <c r="E22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.1675844970219211</v>
       </c>
       <c r="F22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.8379224851096062E-2</v>
       </c>
       <c r="G22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.8750000000000007</v>
       </c>
       <c r="H22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.6302517135428012</v>
       </c>
       <c r="I22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.1895280372440711</v>
       </c>
       <c r="J22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5.9476401862203557E-2</v>
       </c>
       <c r="K22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.6308003020483546</v>
       </c>
       <c r="L22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.1891287136549806</v>
       </c>
       <c r="M22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.9456435682749033E-2</v>
       </c>
       <c r="N22">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.9000000000000008</v>
       </c>
       <c r="O22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.6605185368000019</v>
       </c>
       <c r="P22">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.2107027933794967</v>
       </c>
       <c r="Q22">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.0535139668974836E-2</v>
       </c>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B23">
         <v>18</v>
       </c>
       <c r="C23">
-        <f>C22 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>1.9000000000000008</v>
       </c>
       <c r="D23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.6605254410522492</v>
       </c>
       <c r="E23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2106977914123562</v>
       </c>
       <c r="F23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.0534889570617811E-2</v>
       </c>
       <c r="G23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9250000000000007</v>
       </c>
       <c r="H23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.690792885837558</v>
       </c>
       <c r="I23">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.2318912453297512</v>
       </c>
       <c r="J23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.1594562266487567E-2</v>
       </c>
       <c r="K23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.6913227221854932</v>
       </c>
       <c r="L23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.2315094190956291</v>
       </c>
       <c r="M23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.1575470954781455E-2</v>
       </c>
       <c r="N23">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.9500000000000008</v>
       </c>
       <c r="O23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.7221009120070305</v>
       </c>
       <c r="P23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.2523580316475971</v>
       </c>
       <c r="Q23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.2617901582379856E-2</v>
       </c>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B24">
         <v>19</v>
       </c>
       <c r="C24">
-        <f>C23 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>1.9500000000000008</v>
       </c>
       <c r="D24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.7221075839848385</v>
       </c>
       <c r="E24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2523532515475262</v>
       </c>
       <c r="F24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.2617662577376318E-2</v>
       </c>
       <c r="G24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9750000000000008</v>
       </c>
       <c r="H24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.7534164152735268</v>
       </c>
       <c r="I24">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.2728472539706852</v>
       </c>
       <c r="J24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.3642362698534266E-2</v>
       </c>
       <c r="K24">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.7539287653341056</v>
       </c>
       <c r="L24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.2724825394022088</v>
       </c>
       <c r="M24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.3624126970110439E-2</v>
       </c>
       <c r="N24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.0000000000000009</v>
       </c>
       <c r="O24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.7857317109549489</v>
       </c>
       <c r="P24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.2926574044122896</v>
       </c>
       <c r="Q24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.463287022061448E-2</v>
       </c>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B25">
         <v>20</v>
       </c>
       <c r="C25">
-        <f>C24 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>2.0000000000000009</v>
       </c>
       <c r="D25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.7857381693407186</v>
       </c>
       <c r="E25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2926528391821566</v>
       </c>
       <c r="F25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.4632641959107826E-2</v>
       </c>
       <c r="G25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.0250000000000008</v>
       </c>
       <c r="H25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.8180544903202724</v>
       </c>
       <c r="I25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.3125001559856784</v>
       </c>
       <c r="J25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.5625007799283916E-2</v>
       </c>
       <c r="K25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.8185506732403605</v>
       </c>
       <c r="L25">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.3121520859127063</v>
       </c>
       <c r="M25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.5607604295635322E-2</v>
       </c>
       <c r="N25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.0500000000000007</v>
       </c>
       <c r="O25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.8513457736363539</v>
       </c>
       <c r="P25">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.3317069494658926</v>
       </c>
       <c r="Q25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.6585347473294629E-2</v>
       </c>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B26">
         <v>21</v>
       </c>
       <c r="C26">
-        <f>C25 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>2.0500000000000007</v>
       </c>
       <c r="D26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.8513520382777586</v>
       </c>
       <c r="E26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.331702590914118</v>
       </c>
       <c r="F26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.6585129545705904E-2</v>
       </c>
       <c r="G26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.0750000000000006</v>
       </c>
       <c r="H26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.8846446030506114</v>
       </c>
       <c r="I26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.3509579170056458</v>
       </c>
       <c r="J26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.75478958502823E-2</v>
       </c>
       <c r="K26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.8851259862028997</v>
       </c>
       <c r="L26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.3506259640887479</v>
       </c>
       <c r="M26">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.7531298204437401E-2</v>
       </c>
       <c r="N26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.1000000000000005</v>
       </c>
       <c r="O26">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.918883336482196</v>
       </c>
       <c r="P26">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.3696164374945305</v>
       </c>
       <c r="Q26">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.8480821874726525E-2</v>
       </c>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B27">
         <v>22</v>
       </c>
       <c r="C27">
-        <f>C26 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>2.1000000000000005</v>
       </c>
       <c r="D27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.918889428199404</v>
       </c>
       <c r="E27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.3696122766384611</v>
       </c>
       <c r="F27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.8480613831923054E-2</v>
       </c>
       <c r="G27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.1250000000000004</v>
       </c>
       <c r="H27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.9531297351153656</v>
       </c>
       <c r="I27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.3883321151910311</v>
       </c>
       <c r="J27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.9416605759551553E-2</v>
       </c>
       <c r="K27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.9535977310791797</v>
       </c>
       <c r="L27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.38801571140221</v>
       </c>
       <c r="M27">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.9400785570110507E-2</v>
       </c>
       <c r="N27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.1500000000000004</v>
       </c>
       <c r="O27">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.9882902137695146</v>
       </c>
       <c r="P27">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.406499186655116</v>
       </c>
       <c r="Q27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.0324959332755801E-2</v>
       </c>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B28">
         <v>23</v>
       </c>
       <c r="C28">
-        <f>C27 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>2.1500000000000004</v>
       </c>
       <c r="D28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.988296154170071</v>
       </c>
       <c r="E28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.4064952141142892</v>
       </c>
       <c r="F28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.0324760705714459E-2</v>
       </c>
       <c r="G28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.1750000000000003</v>
       </c>
       <c r="H28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.0234585345229283</v>
       </c>
       <c r="I28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.4247378282561018</v>
       </c>
       <c r="J28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.1236891412805092E-2</v>
       </c>
       <c r="K28">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.0239145998764734</v>
       </c>
       <c r="L28">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.4244363830463338</v>
       </c>
       <c r="M28">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.1221819152316693E-2</v>
       </c>
       <c r="N28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="O28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3.0595179733223876</v>
       </c>
       <c r="P28">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.4424720173999246</v>
       </c>
       <c r="Q28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.2123600869996238E-2</v>
       </c>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B29">
         <v>24</v>
       </c>
       <c r="C29">
-        <f>C28 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="D29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.0595237846210632</v>
       </c>
       <c r="E29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.4424682237812925</v>
       </c>
       <c r="F29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2123411189064623E-2</v>
       </c>
       <c r="G29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.2250000000000001</v>
       </c>
       <c r="H29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.0955854902155955</v>
       </c>
       <c r="I29">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.4602936543674145</v>
       </c>
       <c r="J29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.3014682718370735E-2</v>
       </c>
       <c r="K29">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.0960311259802484</v>
       </c>
       <c r="L29">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.4600065720118751</v>
       </c>
       <c r="M29">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.3000328600593758E-2</v>
       </c>
       <c r="N29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.25</v>
       </c>
       <c r="O29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3.132524113221657</v>
       </c>
       <c r="P29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.4776553364257474</v>
       </c>
       <c r="Q29">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.3882766821287374E-2</v>
       </c>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B30">
         <v>25</v>
       </c>
       <c r="C30">
-        <f>C29 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>2.25</v>
       </c>
       <c r="D30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.1325298180624435</v>
       </c>
       <c r="E30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.4776517127024291</v>
       </c>
       <c r="F30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.3882585635121456E-2</v>
       </c>
       <c r="G30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.2749999999999999</v>
       </c>
       <c r="H30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.169471110880004</v>
       </c>
       <c r="I30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.4951218580320513</v>
       </c>
       <c r="J30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.4756092901602567E-2</v>
       </c>
       <c r="K30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.1699078645132448</v>
       </c>
       <c r="L30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.4948485546217678</v>
       </c>
       <c r="M30">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.4742427731088398E-2</v>
       </c>
       <c r="N30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.2999999999999998</v>
       </c>
       <c r="O30">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3.2072722457935319</v>
       </c>
       <c r="P30">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.512173342989718</v>
       </c>
       <c r="Q30">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.56086671494859E-2</v>
       </c>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B31">
         <v>26</v>
       </c>
       <c r="C31">
-        <f>C30 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>2.2999999999999998</v>
       </c>
       <c r="D31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.2072778670707751</v>
       </c>
       <c r="E31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5121698808741746</v>
       </c>
       <c r="F31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.5608494043708729E-2</v>
       </c>
       <c r="G31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.3249999999999997</v>
       </c>
       <c r="H31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.2450821140926296</v>
       </c>
       <c r="I31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.5293486362734912</v>
       </c>
       <c r="J31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.6467431813674561E-2</v>
       </c>
       <c r="K31">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.2455115829776124</v>
       </c>
       <c r="L31">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.5290885568088082</v>
       </c>
       <c r="M31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.6454427840440417E-2</v>
       </c>
       <c r="N31">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.3499999999999996</v>
       </c>
       <c r="O31">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3.2837322949112155</v>
       </c>
       <c r="P31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.5461543548532526</v>
       </c>
       <c r="Q31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.7307717742662638E-2</v>
       </c>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B32">
         <v>27</v>
       </c>
       <c r="C32">
-        <f>C31 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>2.3499999999999996</v>
       </c>
       <c r="D32">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.283737855586542</v>
       </c>
       <c r="E32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5461510471650062</v>
       </c>
       <c r="F32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.730755235825032E-2</v>
       </c>
       <c r="G32">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.3749999999999996</v>
       </c>
       <c r="H32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.322391631765667</v>
       </c>
       <c r="I32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.5631045042523151</v>
       </c>
       <c r="J32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.8155225212615753E-2</v>
       </c>
       <c r="K32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3228154681928497</v>
       </c>
       <c r="L32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.5628571402920803</v>
       </c>
       <c r="M32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.8142857014604022E-2</v>
       </c>
       <c r="N32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.3999999999999995</v>
       </c>
       <c r="O32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3.3618807126011458</v>
       </c>
       <c r="P32">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.5797312548426332</v>
       </c>
       <c r="Q32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.8986562742131672E-2</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B33">
         <v>28</v>
       </c>
       <c r="C33">
-        <f>C32 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>2.3999999999999995</v>
       </c>
       <c r="D33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.3618862355123458</v>
       </c>
       <c r="E33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5797280958697355</v>
       </c>
       <c r="F33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.8986404793486786E-2</v>
       </c>
       <c r="G33">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.4249999999999994</v>
       </c>
       <c r="H33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.4013794379090894</v>
       </c>
       <c r="I33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.5965248030875112</v>
       </c>
       <c r="J33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.9826240154375561E-2</v>
       </c>
       <c r="K33">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.4017993555895334</v>
       </c>
       <c r="L33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.596289711420575</v>
       </c>
       <c r="M33">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.9814485571028757E-2</v>
       </c>
       <c r="N33">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.4499999999999993</v>
       </c>
       <c r="O33">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3.4417007210833743</v>
       </c>
       <c r="P33">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.6130420625175115</v>
       </c>
       <c r="Q33">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.0652103125875577E-2</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B34">
         <v>29</v>
       </c>
       <c r="C34">
-        <f>C33 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>2.4499999999999993</v>
       </c>
       <c r="D34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.4417062287407076</v>
       </c>
       <c r="E34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.6130390483698842</v>
       </c>
       <c r="F34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8.065195241849421E-2</v>
       </c>
       <c r="G34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.4749999999999992</v>
       </c>
       <c r="H34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.4820322049499546</v>
       </c>
       <c r="I34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.6297503360442551</v>
       </c>
       <c r="J34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8.1487516802212764E-2</v>
       </c>
       <c r="K34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.482449987141814</v>
       </c>
       <c r="L34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.6295271588787092</v>
       </c>
       <c r="M34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8.1476357943935471E-2</v>
       </c>
       <c r="N34">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.4999999999999991</v>
       </c>
       <c r="O34">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3.5231825866846429</v>
       </c>
       <c r="P34">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.6462306387917907</v>
       </c>
       <c r="Q34">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.2311531939589538E-2</v>
       </c>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B35">
         <v>30</v>
       </c>
       <c r="C35">
-        <f>C34 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>2.4999999999999991</v>
       </c>
       <c r="D35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.5231881010491044</v>
       </c>
       <c r="E35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.6462277677432073</v>
       </c>
       <c r="F35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8.2311388387160372E-2</v>
       </c>
       <c r="G35">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.524999999999999</v>
       </c>
       <c r="H35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.5643437952426846</v>
       </c>
       <c r="I35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.6629281425515088</v>
       </c>
       <c r="J35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8.3146407127575442E-2</v>
       </c>
       <c r="K35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.5647613046128921</v>
       </c>
       <c r="L35">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.6627166297637253</v>
       </c>
       <c r="M35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8.3135831488186263E-2</v>
       </c>
       <c r="N35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.5499999999999989</v>
       </c>
       <c r="O35">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3.6063239325372907</v>
       </c>
       <c r="P35">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.6794475346300495</v>
       </c>
       <c r="Q35">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.3972376731502485E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B36">
         <v>31</v>
       </c>
       <c r="C36">
-        <f>C35 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>2.5499999999999989</v>
       </c>
       <c r="D36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.6063294747741352</v>
       </c>
       <c r="E36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.6794448074438488</v>
       </c>
       <c r="F36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8.3972240372192447E-2</v>
       </c>
       <c r="G36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.5749999999999988</v>
       </c>
       <c r="H36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.6483155949602315</v>
       </c>
       <c r="I36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.6962124227706201</v>
       </c>
       <c r="J36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8.4810621138531009E-2</v>
       </c>
       <c r="K36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.6487347853434007</v>
       </c>
       <c r="L36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.6960124568222361</v>
       </c>
       <c r="M36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8.4800622841111811E-2</v>
       </c>
       <c r="N36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.5999999999999988</v>
       </c>
       <c r="O36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3.6911300976152472</v>
       </c>
       <c r="P36">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.7128509982162641</v>
       </c>
       <c r="Q36">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.5642549910813215E-2</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B37">
         <v>32</v>
       </c>
       <c r="C37">
-        <f>C36 + $K$2</f>
+        <f t="shared" si="0"/>
         <v>2.5999999999999988</v>
       </c>
       <c r="D37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.691135687814517</v>
       </c>
       <c r="E37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.7128484184476553</v>
       </c>
       <c r="F37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8.5642420922382778E-2</v>
       </c>
       <c r="G37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.6249999999999987</v>
       </c>
       <c r="H37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.7339568982757085</v>
       </c>
       <c r="I37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.72976562871813</v>
       </c>
       <c r="J37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8.6488281435906506E-2</v>
       </c>
       <c r="K37">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.7343798285324703</v>
       </c>
       <c r="L37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.7295772529361817</v>
       </c>
       <c r="M37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8.6478862646809096E-2</v>
       </c>
       <c r="N37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.6499999999999986</v>
       </c>
       <c r="O37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3.7776145504613261</v>
       </c>
       <c r="P37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.7466081583164663</v>
       </c>
       <c r="Q37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.7330407915823319E-2</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B38">
         <v>33</v>
       </c>
       <c r="C38">
-        <f>C37 + $K$2</f>
+        <f t="shared" ref="C38:C69" si="15">C37 + $K$2</f>
         <v>2.6499999999999986</v>
       </c>
       <c r="D38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.777620207315123</v>
       </c>
       <c r="E38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.7466057325813806</v>
       </c>
       <c r="F38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8.733028662906904E-2</v>
       </c>
       <c r="G38">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.6749999999999985</v>
       </c>
       <c r="H38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.8212853506296574</v>
       </c>
       <c r="I38">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.763759741299024</v>
       </c>
       <c r="J38">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8.8187987064951207E-2</v>
       </c>
       <c r="K38">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.8217142008475986</v>
       </c>
       <c r="L38">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.7635831923239025</v>
       </c>
       <c r="M38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8.817915961619513E-2</v>
       </c>
       <c r="N38">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.6999999999999984</v>
       </c>
       <c r="O38">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3.8657993669313182</v>
       </c>
       <c r="P38">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.7808964049676863</v>
       </c>
       <c r="Q38">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.9044820248384324E-2</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B39">
         <v>34</v>
       </c>
       <c r="C39">
-        <f>C38 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>2.6999999999999984</v>
       </c>
       <c r="D39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.8658051073550808</v>
       </c>
       <c r="E39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.7808941431642147</v>
       </c>
       <c r="F39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8.9044707158210737E-2</v>
       </c>
       <c r="G39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.7249999999999983</v>
       </c>
       <c r="H39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.910327460934186</v>
       </c>
       <c r="I39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.7983777560497156</v>
       </c>
       <c r="J39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8.9918887802485789E-2</v>
       </c>
       <c r="K39">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.9107645512563236</v>
       </c>
       <c r="L39">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.7982135013885343</v>
       </c>
       <c r="M39">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8.9910675069426724E-2</v>
       </c>
       <c r="N39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.7499999999999982</v>
       </c>
       <c r="O39">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3.9557157824245075</v>
       </c>
       <c r="P39">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.8159049921214931</v>
       </c>
       <c r="Q39">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.0795249606074657E-2</v>
       </c>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B40">
         <v>35</v>
       </c>
       <c r="C40">
-        <f>C39 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>2.7499999999999982</v>
       </c>
       <c r="D40">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.9557216211064326</v>
       </c>
       <c r="E40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.8159029075847346</v>
       </c>
       <c r="F40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9.0795145379236733E-2</v>
       </c>
       <c r="G40">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.7749999999999981</v>
       </c>
       <c r="H40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.0011191937960513</v>
       </c>
       <c r="I40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.8338154038987091</v>
       </c>
       <c r="J40">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.1690770194935461E-2</v>
       </c>
       <c r="K40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.0015670062039002</v>
       </c>
       <c r="L40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.8336641856782774</v>
       </c>
       <c r="M40">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9.168320928391388E-2</v>
       </c>
       <c r="N40">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.799999999999998</v>
       </c>
       <c r="O40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4.047404830390346</v>
       </c>
       <c r="P40">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.8518368903969775</v>
       </c>
       <c r="Q40">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.2591844519848879E-2</v>
       </c>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B41">
         <v>36</v>
       </c>
       <c r="C41">
-        <f>C40 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>2.799999999999998</v>
       </c>
       <c r="D41">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.0474107792492298</v>
       </c>
       <c r="E41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.8518349999611439</v>
       </c>
       <c r="F41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9.2591749998057193E-2</v>
       </c>
       <c r="G41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.824999999999998</v>
       </c>
       <c r="H41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.0937066542482583</v>
       </c>
       <c r="I41">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.8702831367359301</v>
       </c>
       <c r="J41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.3514156836796508E-2</v>
       </c>
       <c r="K41">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.0941678576676281</v>
       </c>
       <c r="L41">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.8701460229284457</v>
       </c>
       <c r="M41">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9.3507301146422292E-2</v>
       </c>
       <c r="N41">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.8499999999999979</v>
       </c>
       <c r="O41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4.140918080395652</v>
       </c>
       <c r="P41">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.8889109215173214</v>
       </c>
       <c r="Q41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.4445546075866083E-2</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B42">
         <v>37</v>
       </c>
       <c r="C42">
-        <f>C41 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>2.8499999999999979</v>
       </c>
       <c r="D42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.1409241479226235</v>
       </c>
       <c r="E42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.8889092454496468</v>
       </c>
       <c r="F42">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9.444546227248235E-2</v>
       </c>
       <c r="G42">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.8749999999999978</v>
       </c>
       <c r="H42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.1881468790588645</v>
       </c>
       <c r="I42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.9080084108461095</v>
       </c>
       <c r="J42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.5400420542305478E-2</v>
       </c>
       <c r="K42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.1886243581937759</v>
       </c>
       <c r="L42">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.9078868554375459</v>
       </c>
       <c r="M42">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9.5394342771877305E-2</v>
       </c>
       <c r="N42">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.8999999999999977</v>
       </c>
       <c r="O42">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4.2363184906945008</v>
       </c>
       <c r="P42">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.9273642090520815</v>
       </c>
       <c r="Q42">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.6368210452604075E-2</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B43">
         <v>38</v>
       </c>
       <c r="C43">
-        <f>C42 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>2.8999999999999977</v>
       </c>
       <c r="D43">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.2363246811481989</v>
       </c>
       <c r="E43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.9273627708107797</v>
       </c>
       <c r="F43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9.6368138540538995E-2</v>
       </c>
       <c r="G43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.9249999999999976</v>
       </c>
       <c r="H43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.2845087504184685</v>
       </c>
       <c r="I43">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.9472383039597543</v>
       </c>
       <c r="J43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.7361915197987717E-2</v>
       </c>
       <c r="K43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.2850056387471929</v>
       </c>
       <c r="L43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.9471342177362869</v>
       </c>
       <c r="M43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9.7356710886814357E-2</v>
       </c>
       <c r="N43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.9499999999999975</v>
       </c>
       <c r="O43">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4.3336813920350137</v>
       </c>
       <c r="P43">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.967454982308521</v>
       </c>
       <c r="Q43">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.8372749115426053E-2</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B44">
         <v>39</v>
       </c>
       <c r="C44">
-        <f>C43 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>2.9499999999999975</v>
       </c>
       <c r="D44">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.3336877044524602</v>
       </c>
       <c r="E44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.9674538080608519</v>
       </c>
       <c r="F44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9.8372690403042598E-2</v>
       </c>
       <c r="G44">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.9749999999999974</v>
       </c>
       <c r="H44">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.3828740496539815</v>
       </c>
       <c r="I44">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.9882425032262865</v>
       </c>
       <c r="J44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.9412125161314327E-2</v>
       </c>
       <c r="K44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.3833937670331178</v>
       </c>
       <c r="L44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.9881583370500553</v>
       </c>
       <c r="M44">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9.9407916852502776E-2</v>
       </c>
       <c r="N44">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.9999999999999973</v>
       </c>
       <c r="O44">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4.4330956213049628</v>
       </c>
       <c r="P44">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.0094657708663028</v>
       </c>
       <c r="Q44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.10047328854331515</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B45">
         <v>40</v>
       </c>
       <c r="C45">
-        <f>C44 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>2.9999999999999973</v>
       </c>
       <c r="D45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.4331020482814587</v>
       </c>
       <c r="E45">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.0094648886817286</v>
       </c>
       <c r="F45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.10047324443408644</v>
       </c>
       <c r="G45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.0249999999999972</v>
       </c>
       <c r="H45">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.4833386704985019</v>
       </c>
       <c r="I45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.0313167008868764</v>
       </c>
       <c r="J45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.10156583504434383</v>
       </c>
       <c r="K45">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.4838849658036306</v>
       </c>
       <c r="L45">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.0312555434872186</v>
       </c>
       <c r="M45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.10156277717436094</v>
       </c>
       <c r="N45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.0499999999999972</v>
       </c>
       <c r="O45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4.5346648254558195</v>
       </c>
       <c r="P45">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.0537070251554148</v>
       </c>
       <c r="Q45">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.10268535125777074</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B46">
         <v>41</v>
       </c>
       <c r="C46">
-        <f>C45 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>3.0499999999999972</v>
       </c>
       <c r="D46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.5346713516363364</v>
       </c>
       <c r="E46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.053706463761662</v>
       </c>
       <c r="F46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.1026853231880831</v>
       </c>
       <c r="G46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.0749999999999971</v>
       </c>
       <c r="H46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.5860140132303782</v>
       </c>
       <c r="I46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.0767864303651242</v>
       </c>
       <c r="J46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.10383932151825621</v>
       </c>
       <c r="K46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.5865910123954645</v>
       </c>
       <c r="L46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.0767521227316896</v>
       </c>
       <c r="M46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.10383760613658449</v>
       </c>
       <c r="N46">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.099999999999997</v>
       </c>
       <c r="O46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4.6385089577729213</v>
       </c>
       <c r="P46">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.1005211918193987</v>
       </c>
       <c r="Q46">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.10502605959096994</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B47">
         <v>42</v>
       </c>
       <c r="C47">
-        <f>C46 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>3.099999999999997</v>
       </c>
       <c r="D47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.6385155579844586</v>
       </c>
       <c r="E47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.100520978774727</v>
       </c>
       <c r="F47">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.10502604893873635</v>
       </c>
       <c r="G47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.1249999999999969</v>
       </c>
       <c r="H47">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.6910285824538267</v>
       </c>
       <c r="I47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.1250113656715177</v>
       </c>
       <c r="J47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.10625056828357589</v>
       </c>
       <c r="K47">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.6916408421262465</v>
       </c>
       <c r="L47">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.1250086340139882</v>
       </c>
       <c r="M47">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.10625043170069942</v>
       </c>
       <c r="N47">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.1499999999999968</v>
       </c>
       <c r="O47">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4.7447659896851579</v>
       </c>
       <c r="P47">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.150287258615561</v>
       </c>
       <c r="Q47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.10751436293077805</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B48">
         <v>43</v>
       </c>
       <c r="C48">
-        <f>C47 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>3.1499999999999968</v>
       </c>
       <c r="D48">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.7447726266241359</v>
       </c>
       <c r="E48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.1502874177075357</v>
       </c>
       <c r="F48">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.1075143708853768</v>
       </c>
       <c r="G48">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.1749999999999967</v>
       </c>
       <c r="H48">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.7985298120668247</v>
       </c>
       <c r="I48">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.1763900880575546</v>
       </c>
       <c r="J48">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.10881950440287774</v>
       </c>
       <c r="K48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.7991823788255745</v>
       </c>
       <c r="L48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.1764246968536041</v>
       </c>
       <c r="M48">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.10882123484268021</v>
       </c>
       <c r="N48">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.1999999999999966</v>
       </c>
       <c r="O48">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4.8535938614668162</v>
       </c>
       <c r="P48">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.2034257581152756</v>
       </c>
       <c r="Q48">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.11017128790576379</v>
       </c>
     </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B49">
         <v>44</v>
       </c>
       <c r="C49">
-        <f>C48 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>3.1999999999999966</v>
       </c>
       <c r="D49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.8536004828378454</v>
       </c>
       <c r="E49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.2034263057441379</v>
       </c>
       <c r="F49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.1101713152872069</v>
       </c>
       <c r="G49">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.2249999999999965</v>
       </c>
       <c r="H49">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.908686140481449</v>
       </c>
       <c r="I49">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.2313652907103014</v>
       </c>
       <c r="J49">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.11156826453551508</v>
       </c>
       <c r="K49">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.9093846151056031</v>
       </c>
       <c r="L49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.2314442163811901</v>
       </c>
       <c r="M49">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.11157221081905951</v>
       </c>
       <c r="N49">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.2499999999999964</v>
       </c>
       <c r="O49">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4.9651726936569052</v>
       </c>
       <c r="P49">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.2604041762845535</v>
       </c>
       <c r="Q49">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.11302020881422768</v>
       </c>
     </row>
-    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B50">
         <v>45</v>
       </c>
       <c r="C50">
-        <f>C49 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>3.2499999999999964</v>
       </c>
       <c r="D50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.9651792286396095</v>
       </c>
       <c r="E50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.2604051165283661</v>
       </c>
       <c r="F50">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.11302025582641831</v>
       </c>
       <c r="G50">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.2749999999999964</v>
       </c>
       <c r="H50">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.0216893565528187</v>
       </c>
       <c r="I50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.2904293374831037</v>
       </c>
       <c r="J50">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.11452146687415519</v>
       </c>
       <c r="K50">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.0224399620766871</v>
       </c>
       <c r="L50">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.2905609613812699</v>
       </c>
       <c r="M50">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.1145280480690635</v>
       </c>
       <c r="N50">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.2999999999999963</v>
       </c>
       <c r="O50">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5.0797072767086728</v>
       </c>
       <c r="P50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.3217426420358129</v>
       </c>
       <c r="Q50">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.11608713210179065</v>
       </c>
     </row>
-    <row r="51" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B51">
         <v>46</v>
       </c>
       <c r="C51">
-        <f>C50 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>3.2999999999999963</v>
       </c>
       <c r="D51">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.0797136316087173</v>
       </c>
       <c r="E51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.321743960027848</v>
       </c>
       <c r="F51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.1160871980013924</v>
       </c>
       <c r="G51">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.3249999999999962</v>
       </c>
       <c r="H51">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.137757230609413</v>
       </c>
       <c r="I51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.3541300043026205</v>
       </c>
       <c r="J51">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.11770650021513103</v>
       </c>
       <c r="K51">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.1385668817162831</v>
       </c>
       <c r="L51">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.3543243204673301</v>
       </c>
       <c r="M51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.11771621602336652</v>
       </c>
       <c r="N51">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.3499999999999961</v>
       </c>
       <c r="O51">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5.1974298476320842</v>
       </c>
       <c r="P51">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.3880196638170359</v>
       </c>
       <c r="Q51">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.11940098319085179</v>
       </c>
     </row>
-    <row r="52" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B52">
         <v>47</v>
       </c>
       <c r="C52">
-        <f>C51 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>3.3499999999999961</v>
       </c>
       <c r="D52">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.1974359005535904</v>
       </c>
       <c r="E52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.3880213170008058</v>
       </c>
       <c r="F52">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.11940106585004029</v>
       </c>
       <c r="G52">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.374999999999996</v>
       </c>
       <c r="H52">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.2571364334786104</v>
       </c>
       <c r="I52">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.4230760962506417</v>
       </c>
       <c r="J52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.12115380481253209</v>
       </c>
       <c r="K52">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2580128029598567</v>
       </c>
       <c r="L52">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.4233449240525586</v>
       </c>
       <c r="M52">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.12116724620262793</v>
       </c>
       <c r="N52">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.3999999999999959</v>
       </c>
       <c r="O52">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5.3186031467562183</v>
       </c>
       <c r="P52">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.4598775103375252</v>
       </c>
       <c r="Q52">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.12299387551687627</v>
       </c>
     </row>
-    <row r="53" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B53">
         <v>48</v>
       </c>
       <c r="C53">
-        <f>C52 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>3.3999999999999959</v>
       </c>
       <c r="D53">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.3186087411197969</v>
       </c>
       <c r="E53">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.4598794171170542</v>
       </c>
       <c r="F53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.12299397085585272</v>
       </c>
       <c r="G53">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.4249999999999958</v>
       </c>
       <c r="H53">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.3801057265477228</v>
       </c>
       <c r="I53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.4979424271231405</v>
       </c>
       <c r="J53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.12489712135615703</v>
       </c>
       <c r="K53">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.3810573017978758</v>
       </c>
       <c r="L53">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.498299610433703</v>
       </c>
       <c r="M53">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.12491498052168515</v>
       </c>
       <c r="N53">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.4499999999999957</v>
       </c>
       <c r="O53">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5.4435237216414816</v>
       </c>
       <c r="P53">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.5380265781545397</v>
       </c>
       <c r="Q53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.12690132890772698</v>
       </c>
     </row>
-    <row r="54" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B54">
         <v>49</v>
       </c>
       <c r="C54">
-        <f>C53 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>3.4499999999999957</v>
       </c>
       <c r="D54">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.4435286583730074</v>
       </c>
       <c r="E54">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.5380286034562434</v>
       </c>
       <c r="F54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.12690143017281216</v>
       </c>
       <c r="G54">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.4749999999999956</v>
       </c>
       <c r="H54">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.506979373459413</v>
       </c>
       <c r="I54">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.5794733407363224</v>
       </c>
       <c r="J54">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.12897366703681612</v>
       </c>
       <c r="K54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.508015491891415</v>
       </c>
       <c r="L54">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.5799349022006366</v>
       </c>
       <c r="M54">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.12899674511003184</v>
       </c>
       <c r="N54">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.4999999999999956</v>
       </c>
       <c r="O54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5.5725254034830396</v>
       </c>
       <c r="P54">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.6232477130757497</v>
       </c>
       <c r="Q54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.13116238565378749</v>
       </c>
     </row>
-    <row r="55" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B55">
         <v>50</v>
       </c>
       <c r="C55">
-        <f>C54 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>3.4999999999999956</v>
       </c>
       <c r="D55">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.57252943172639</v>
       </c>
       <c r="E55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.6232496504351981</v>
       </c>
       <c r="F55">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.13116248252175991</v>
       </c>
       <c r="G55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.5249999999999955</v>
       </c>
       <c r="H55">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.6381106729872696</v>
       </c>
       <c r="I55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.6684835032764695</v>
       </c>
       <c r="J55">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.13342417516382349</v>
       </c>
       <c r="K55">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.6392415193083014</v>
       </c>
       <c r="L55">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.6690677028193233</v>
       </c>
       <c r="M55">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.13345338514096616</v>
       </c>
       <c r="N55">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.5499999999999954</v>
       </c>
       <c r="O55">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5.7059828168673565</v>
       </c>
       <c r="P55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.7163909083128339</v>
       </c>
       <c r="Q55">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.1358195454156417</v>
       </c>
     </row>
-    <row r="56" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B56">
         <v>51</v>
       </c>
       <c r="C56">
-        <f>C55 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>3.5499999999999954</v>
       </c>
       <c r="D56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.7059856231508865</v>
       </c>
       <c r="E56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.7163924583804397</v>
       </c>
       <c r="F56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.135819622919022</v>
       </c>
       <c r="G56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.5749999999999953</v>
       </c>
       <c r="H56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.7738954346103979</v>
       </c>
       <c r="I56">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.765854051555638</v>
       </c>
       <c r="J56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.1382927025777819</v>
       </c>
       <c r="K56">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.7751319744397778</v>
       </c>
       <c r="L56">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.7665812703263342</v>
       </c>
       <c r="M56">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.13832906351631671</v>
       </c>
       <c r="N56">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.5999999999999952</v>
       </c>
       <c r="O56">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5.8443146866672029</v>
       </c>
       <c r="P56">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.8183680331923799</v>
       </c>
       <c r="Q56">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.140918401659619</v>
       </c>
     </row>
-    <row r="57" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B57">
         <v>52</v>
       </c>
       <c r="C57">
-        <f>C56 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>3.5999999999999952</v>
       </c>
       <c r="D57">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.8443158826120261</v>
       </c>
       <c r="E57">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.8183687791514487</v>
       </c>
       <c r="F57">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.14091843895757244</v>
       </c>
       <c r="G57">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.6249999999999951</v>
       </c>
       <c r="H57">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.9147751020908119</v>
       </c>
       <c r="I57">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.8725212830886604</v>
       </c>
       <c r="J57">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.14362606415443302</v>
       </c>
       <c r="K57">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.9161289146892422</v>
       </c>
       <c r="L57">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.87341361579506</v>
       </c>
       <c r="M57">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.14367068078975301</v>
       </c>
       <c r="N57">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.649999999999995</v>
       </c>
       <c r="O57">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5.9879865634017788</v>
       </c>
       <c r="P57">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.9301361915206234</v>
       </c>
       <c r="Q57">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.14650680957603118</v>
       </c>
     </row>
-    <row r="58" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B58">
         <v>53</v>
       </c>
       <c r="C58">
-        <f>C57 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>3.649999999999995</v>
       </c>
       <c r="D58">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.9879856723490219</v>
       </c>
       <c r="E58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.9301355730275267</v>
       </c>
       <c r="F58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.14650677865137635</v>
       </c>
       <c r="G58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.6749999999999949</v>
       </c>
       <c r="H58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6.0612390616747103</v>
       </c>
       <c r="I58">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.9894538632581309</v>
       </c>
       <c r="J58">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.14947269316290654</v>
       </c>
       <c r="K58">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6.0627220189304749</v>
       </c>
       <c r="L58">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.9905342528383541</v>
       </c>
       <c r="M58">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.14952671264191772</v>
       </c>
       <c r="N58">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.6999999999999948</v>
       </c>
       <c r="O58">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6.1375123849909397</v>
       </c>
       <c r="P58">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.0526669225130512</v>
       </c>
       <c r="Q58">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.15263334612565257</v>
       </c>
     </row>
-    <row r="59" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B59">
         <v>54</v>
       </c>
       <c r="C59">
-        <f>C58 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>3.6999999999999948</v>
       </c>
       <c r="D59">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.137508828413468</v>
       </c>
       <c r="E59">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.0526642116680232</v>
       </c>
       <c r="F59">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.15263321058340118</v>
       </c>
       <c r="G59">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.7249999999999948</v>
       </c>
       <c r="H59">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6.2138254337051686</v>
       </c>
       <c r="I59">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.1176129752660433</v>
       </c>
       <c r="J59">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.15588064876330218</v>
       </c>
       <c r="K59">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6.2154491527951192</v>
       </c>
       <c r="L59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.1189036676751138</v>
       </c>
       <c r="M59">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.15594518338375571</v>
       </c>
       <c r="N59">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.7499999999999947</v>
       </c>
       <c r="O59">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6.2934540117972233</v>
       </c>
       <c r="P59">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.1868947490837929</v>
       </c>
       <c r="Q59">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.15934473745418964</v>
       </c>
     </row>
-    <row r="60" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B60">
         <v>55</v>
       </c>
       <c r="C60">
-        <f>C59 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>3.7499999999999947</v>
       </c>
       <c r="D60">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.2934470971354193</v>
       </c>
       <c r="E60">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.1868890349231709</v>
       </c>
       <c r="F60">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.15934445174615855</v>
       </c>
       <c r="G60">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.7749999999999946</v>
       </c>
       <c r="H60">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6.3731193230084981</v>
       </c>
       <c r="I60">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.2578880098157552</v>
       </c>
       <c r="J60">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.16289440049078777</v>
       </c>
       <c r="K60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6.3748942973808136</v>
       </c>
       <c r="L60">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.259408055672981</v>
       </c>
       <c r="M60">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.16297040278364905</v>
       </c>
       <c r="N60">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.7999999999999945</v>
       </c>
       <c r="O60">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6.456417499919068</v>
       </c>
       <c r="P60">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.3336366936387423</v>
       </c>
       <c r="Q60">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.16668183468193712</v>
       </c>
     </row>
-    <row r="61" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B61">
         <v>56</v>
       </c>
       <c r="C61">
-        <f>C60 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>3.7999999999999945</v>
       </c>
       <c r="D61">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.4564064126315808</v>
       </c>
       <c r="E61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.3336268859274307</v>
       </c>
       <c r="F61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.16668134429637155</v>
       </c>
       <c r="G61">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.8249999999999944</v>
       </c>
       <c r="H61">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6.5397470847797665</v>
       </c>
       <c r="I61">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.4109985367485129</v>
       </c>
       <c r="J61">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.17054992683742565</v>
       </c>
       <c r="K61">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6.5416813760502937</v>
       </c>
       <c r="L61">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.4127600494772952</v>
       </c>
       <c r="M61">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.17063800247386476</v>
       </c>
       <c r="N61">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.8499999999999943</v>
       </c>
       <c r="O61">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6.6270444151054457</v>
       </c>
       <c r="P61">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.4934727430995012</v>
       </c>
       <c r="Q61">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.17467363715497508</v>
       </c>
     </row>
-    <row r="62" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B62">
         <v>57</v>
       </c>
       <c r="C62">
-        <f>C61 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>3.8499999999999943</v>
       </c>
       <c r="D62">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.627028219310569</v>
       </c>
       <c r="E62">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.4934576116593115</v>
       </c>
       <c r="F62">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.1746728805829656</v>
       </c>
       <c r="G62">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.8749999999999942</v>
       </c>
       <c r="H62">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6.7143646596020519</v>
       </c>
       <c r="I62">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.5773520446200955</v>
       </c>
       <c r="J62">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.17886760223100479</v>
       </c>
       <c r="K62">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6.7164620204260714</v>
       </c>
       <c r="L62">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.5793549972325516</v>
       </c>
       <c r="M62">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.17896774986162758</v>
       </c>
       <c r="N62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.8999999999999941</v>
       </c>
       <c r="O62">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6.805995969172197</v>
       </c>
       <c r="P62">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.6665767718184643</v>
       </c>
       <c r="Q62">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.18332883859092322</v>
       </c>
     </row>
-    <row r="63" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B63">
         <v>58</v>
       </c>
       <c r="C63">
-        <f>C62 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>3.8999999999999941</v>
       </c>
       <c r="D63">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.8059736232037613</v>
       </c>
       <c r="E63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.6665550432104488</v>
       </c>
       <c r="F63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.18332775216052244</v>
       </c>
       <c r="G63">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.924999999999994</v>
       </c>
       <c r="H63">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6.8976374992840226</v>
       </c>
       <c r="I63">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.756847527094028</v>
       </c>
       <c r="J63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.18784237635470141</v>
       </c>
       <c r="K63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6.8998948113811123</v>
       </c>
       <c r="L63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.7590731238374606</v>
       </c>
       <c r="M63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.18795365619187304</v>
       </c>
       <c r="N63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.949999999999994</v>
       </c>
       <c r="O63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6.993927279395634</v>
       </c>
       <c r="P63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.8524898157139202</v>
       </c>
       <c r="Q63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.19262449078569602</v>
       </c>
     </row>
-    <row r="64" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B64">
         <v>59</v>
       </c>
       <c r="C64">
-        <f>C63 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>3.949999999999994</v>
       </c>
       <c r="D64">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.9938976745436561</v>
       </c>
       <c r="E64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.8524603519857972</v>
       </c>
       <c r="F64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.19262301759928988</v>
       </c>
       <c r="G64">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.9749999999999939</v>
       </c>
       <c r="H64">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7.0902091833433012</v>
       </c>
       <c r="I64">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.9486195905142956</v>
       </c>
       <c r="J64">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.19743097952571478</v>
       </c>
       <c r="K64">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7.0926131643065133</v>
       </c>
       <c r="L64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.9510228087486094</v>
       </c>
       <c r="M64">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.19755114043743049</v>
       </c>
       <c r="N64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.9999999999999938</v>
       </c>
       <c r="O64">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7.1914488149810865</v>
       </c>
       <c r="P64">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.0498355099062495</v>
       </c>
       <c r="Q64">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.2024917754953125</v>
       </c>
     </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B65">
         <v>60</v>
       </c>
       <c r="C65">
-        <f>C64 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>3.9999999999999938</v>
       </c>
       <c r="D65">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.1914108467138051</v>
       </c>
       <c r="E65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.0497975887809448</v>
       </c>
       <c r="F65">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.20248987943904725</v>
       </c>
       <c r="G65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.0249999999999941</v>
       </c>
       <c r="H65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7.292655786433329</v>
       </c>
       <c r="I65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.1507295006569418</v>
       </c>
       <c r="J65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.20753647503284711</v>
       </c>
       <c r="K65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7.2951790842302291</v>
       </c>
       <c r="L65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.15323237205937</v>
       </c>
       <c r="M65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.2076616186029685</v>
       </c>
       <c r="N65">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.0499999999999936</v>
       </c>
       <c r="O65">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7.3990724653167739</v>
       </c>
       <c r="P65">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.2559944184128868</v>
       </c>
       <c r="Q65">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.21279972092064436</v>
       </c>
     </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B66">
         <v>61</v>
       </c>
       <c r="C66">
-        <f>C65 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>4.0499999999999936</v>
       </c>
       <c r="D66">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.3990251446523594</v>
       </c>
       <c r="E66">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.2559481123962666</v>
       </c>
       <c r="F66">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.21279740561981333</v>
       </c>
       <c r="G66">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.074999999999994</v>
       </c>
       <c r="H66">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7.5054238474622661</v>
       </c>
       <c r="I66">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.3598320287257231</v>
       </c>
       <c r="J66">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.21799160143628615</v>
       </c>
       <c r="K66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7.508020945370502</v>
       </c>
       <c r="L66">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.3623205848170894</v>
       </c>
       <c r="M66">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.21811602924085449</v>
       </c>
       <c r="N66">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.0999999999999934</v>
       </c>
       <c r="O66">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7.6171411738932138</v>
       </c>
       <c r="P66">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.4667828762825241</v>
       </c>
       <c r="Q66">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.22333914381412623</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B67">
         <v>62</v>
       </c>
       <c r="C67">
-        <f>C66 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>4.0999999999999934</v>
       </c>
       <c r="D67">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.6170837797837292</v>
       </c>
       <c r="E67">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.4667294815610834</v>
       </c>
       <c r="F67">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.22333647407805418</v>
       </c>
       <c r="G67">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.1249999999999938</v>
       </c>
       <c r="H67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7.7287520168227566</v>
       </c>
       <c r="I67">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.5708819732485697</v>
       </c>
       <c r="J67">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.2285440986624285</v>
       </c>
       <c r="K67">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7.7313558291149436</v>
       </c>
       <c r="L67">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.5732111100496455</v>
       </c>
       <c r="M67">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.22866055550248229</v>
       </c>
       <c r="N67">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.1499999999999932</v>
       </c>
       <c r="O67">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7.8457443352862111</v>
       </c>
       <c r="P67">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.6762221245843065</v>
       </c>
       <c r="Q67">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.23381110622921533</v>
       </c>
     </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B68">
         <v>63</v>
       </c>
       <c r="C68">
-        <f>C67 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>4.1499999999999932</v>
       </c>
       <c r="D68">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.8456765945565774</v>
       </c>
       <c r="E68">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.6761645202405981</v>
       </c>
       <c r="F68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.23380822601202991</v>
       </c>
       <c r="G68">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.1749999999999936</v>
       </c>
       <c r="H68">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7.9625807075625925</v>
       </c>
       <c r="I68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.7769876986248034</v>
       </c>
       <c r="J68">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.23884938493124019</v>
       </c>
       <c r="K68">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7.9651012870221978</v>
       </c>
       <c r="L68">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.7789984803941055</v>
       </c>
       <c r="M68">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.23894992401970527</v>
       </c>
       <c r="N68">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.1999999999999931</v>
       </c>
       <c r="O68">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>8.0846265185762825</v>
       </c>
       <c r="P68">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.8765252189110528</v>
       </c>
       <c r="Q68">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.24382626094555265</v>
       </c>
     </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B69">
         <v>64</v>
       </c>
       <c r="C69">
-        <f>C68 + $K$2</f>
+        <f t="shared" si="15"/>
         <v>4.1999999999999931</v>
       </c>
       <c r="D69">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.0845487786998227</v>
       </c>
       <c r="E69">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.8764679677086056</v>
       </c>
       <c r="F69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.2438233983854303</v>
       </c>
       <c r="G69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.2249999999999934</v>
       </c>
       <c r="H69">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.2064604778925379</v>
       </c>
       <c r="I69">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.9695548911021046</v>
       </c>
       <c r="J69">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.24847774455510524</v>
       </c>
       <c r="K69">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8.2087876509773761</v>
       </c>
       <c r="L69">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.971106404103832</v>
       </c>
       <c r="M69">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.24855532020519161</v>
       </c>
       <c r="N69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.2499999999999929</v>
       </c>
       <c r="O69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>8.3331040989050145</v>
       </c>
       <c r="P69">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5.0584486099933947</v>
       </c>
       <c r="Q69">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.25292243049966973</v>
       </c>
     </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B70">
         <v>65</v>
       </c>
       <c r="C70">
-        <f>C69 + $K$2</f>
+        <f t="shared" ref="C70:C85" si="16">C69 + $K$2</f>
         <v>4.2499999999999929</v>
       </c>
       <c r="D70">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.3330174384341049</v>
       </c>
       <c r="E70">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.0583976014841028</v>
       </c>
       <c r="F70">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.25291988007420513</v>
       </c>
       <c r="G70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.2749999999999932</v>
       </c>
       <c r="H70">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.4594773784712078</v>
       </c>
       <c r="I70">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.1388609430842438</v>
       </c>
       <c r="J70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.25694304715421218</v>
       </c>
       <c r="K70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8.4614889620112113</v>
       </c>
       <c r="L70">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5.1398724903001245</v>
       </c>
       <c r="M70">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.25699362451500624</v>
       </c>
       <c r="N70">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.2999999999999927</v>
       </c>
       <c r="O70">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>8.5900110629491113</v>
       </c>
       <c r="P70">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5.2121167390096872</v>
       </c>
       <c r="Q70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.26060583695048439</v>
       </c>
     </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B71">
         <v>66</v>
       </c>
       <c r="C71">
-        <f>C70 + $K$2</f>
+        <f t="shared" si="16"/>
         <v>4.2999999999999927</v>
       </c>
       <c r="D71">
-        <f t="shared" ref="D71:D85" si="14">D70 + (F70 + 2*J70 + 2*M70 + Q70)/6</f>
+        <f t="shared" ref="D71:D85" si="17">D70 + (F70 + 2*J70 + 2*M70 + Q70)/6</f>
         <v>8.5899172818279599</v>
       </c>
       <c r="E71">
-        <f t="shared" ref="E71:E85" si="15">SIN(C71 - D71) + C71</f>
+        <f t="shared" ref="E71:E85" si="18">SIN(C71 - D71) + C71</f>
         <v>5.212078291252344</v>
       </c>
       <c r="F71">
-        <f t="shared" ref="F71:F85" si="16">$K$2 * E71</f>
+        <f t="shared" ref="F71:F85" si="19">$K$2 * E71</f>
         <v>0.26060391456261722</v>
       </c>
       <c r="G71">
-        <f t="shared" ref="G71:G85" si="17">C71 + $K$2 / 2</f>
+        <f t="shared" ref="G71:G85" si="20">C71 + $K$2 / 2</f>
         <v>4.3249999999999931</v>
       </c>
       <c r="H71">
-        <f t="shared" ref="H71:H85" si="18">D71 + F71 / 2</f>
+        <f t="shared" ref="H71:H85" si="21">D71 + F71 / 2</f>
         <v>8.7202192391092677</v>
       </c>
       <c r="I71">
-        <f t="shared" ref="I71:I85" si="19">SIN(G71 - H71) + G71</f>
+        <f t="shared" ref="I71:I85" si="22">SIN(G71 - H71) + G71</f>
         <v>5.2751219197881847</v>
       </c>
       <c r="J71">
-        <f t="shared" ref="J71:J85" si="20">$K$2 * I71</f>
+        <f t="shared" ref="J71:J85" si="23">$K$2 * I71</f>
         <v>0.26375609598940924</v>
       </c>
       <c r="K71">
-        <f t="shared" ref="K71:K85" si="21">D71 + J71/2</f>
+        <f t="shared" ref="K71:K85" si="24">D71 + J71/2</f>
         <v>8.7217953298226654</v>
       </c>
       <c r="L71">
-        <f t="shared" ref="L71:L85" si="22">SIN(G71 - K71) + G71</f>
+        <f t="shared" ref="L71:L85" si="25">SIN(G71 - K71) + G71</f>
         <v>5.2756122886622876</v>
       </c>
       <c r="M71">
-        <f t="shared" ref="M71:M85" si="23" xml:space="preserve"> $K$2 * L71</f>
+        <f t="shared" ref="M71:M85" si="26" xml:space="preserve"> $K$2 * L71</f>
         <v>0.2637806144331144</v>
       </c>
       <c r="N71">
-        <f t="shared" ref="N71:N85" si="24">C71 + $K$2</f>
+        <f t="shared" ref="N71:N85" si="27">C71 + $K$2</f>
         <v>4.3499999999999925</v>
       </c>
       <c r="O71">
-        <f t="shared" ref="O71:O85" si="25">D71 + M71</f>
+        <f t="shared" ref="O71:O85" si="28">D71 + M71</f>
         <v>8.8536978962610746</v>
       </c>
       <c r="P71">
-        <f t="shared" ref="P71:P85" si="26">SIN(N71 - O71) + N71</f>
+        <f t="shared" ref="P71:P85" si="29">SIN(N71 - O71) + N71</f>
         <v>5.3283029333078478</v>
       </c>
       <c r="Q71">
-        <f t="shared" ref="Q71:Q85" si="27">$K$2 * P71</f>
+        <f t="shared" ref="Q71:Q85" si="30">$K$2 * P71</f>
         <v>0.2664151466653924</v>
       </c>
     </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B72">
         <v>67</v>
       </c>
       <c r="C72">
-        <f>C71 + $K$2</f>
+        <f t="shared" si="16"/>
         <v>4.3499999999999925</v>
       </c>
       <c r="D72">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>8.853599362173469</v>
       </c>
       <c r="E72">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>5.3282825143096684</v>
       </c>
       <c r="F72">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.26641412571548345</v>
       </c>
       <c r="G72">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>4.3749999999999929</v>
       </c>
       <c r="H72">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>8.9868064250312099</v>
       </c>
       <c r="I72">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>5.3699458379523399</v>
       </c>
       <c r="J72">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0.26849729189761701</v>
       </c>
       <c r="K72">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>8.9878480081222776</v>
       </c>
       <c r="L72">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>5.3700498867568864</v>
       </c>
       <c r="M72">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.26850249433784434</v>
       </c>
       <c r="N72">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>4.3999999999999924</v>
       </c>
       <c r="O72">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>9.1221018565113141</v>
       </c>
       <c r="P72">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>5.3999528303895001</v>
       </c>
       <c r="Q72">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.26999764151947503</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B73">
         <v>68</v>
       </c>
       <c r="C73">
-        <f>C72 + $K$2</f>
+        <f t="shared" si="16"/>
         <v>4.3999999999999924</v>
       </c>
       <c r="D73">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>9.1220012521244485</v>
       </c>
       <c r="E73">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>5.3999538024716989</v>
       </c>
       <c r="F73">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.26999769012358493</v>
       </c>
       <c r="G73">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>4.4249999999999927</v>
       </c>
       <c r="H73">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>9.257000097186241</v>
       </c>
       <c r="I73">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>5.4178551148474536</v>
       </c>
       <c r="J73">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0.2708927557423727</v>
       </c>
       <c r="K73">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>9.2574476299956352</v>
       </c>
       <c r="L73">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>5.4178016130719593</v>
       </c>
       <c r="M73">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.27089008065359799</v>
       </c>
       <c r="N73">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>4.4499999999999922</v>
       </c>
       <c r="O73">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>9.3928913327780457</v>
       </c>
       <c r="P73">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>5.4235517470993893</v>
       </c>
       <c r="Q73">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.2711775873549695</v>
       </c>
     </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B74">
         <v>69</v>
       </c>
       <c r="C74">
-        <f>C73 + $K$2</f>
+        <f t="shared" si="16"/>
         <v>4.4499999999999922</v>
       </c>
       <c r="D74">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>9.3927914105028645</v>
       </c>
       <c r="E74">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>5.4235745711434689</v>
       </c>
       <c r="F74">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.27117872855717345</v>
       </c>
       <c r="G74">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>4.4749999999999925</v>
       </c>
       <c r="H74">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>9.5283807747814517</v>
       </c>
       <c r="I74">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>5.4174234512800199</v>
       </c>
       <c r="J74">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0.27087117256400101</v>
       </c>
       <c r="K74">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>9.5282269967848645</v>
       </c>
       <c r="L74">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>5.4174748668737447</v>
       </c>
       <c r="M74">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.27087374334368725</v>
       </c>
       <c r="N74">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>4.499999999999992</v>
       </c>
       <c r="O74">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>9.6636651538465514</v>
       </c>
       <c r="P74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>5.3998912777894832</v>
       </c>
       <c r="Q74">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.26999456388947418</v>
       </c>
     </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B75">
         <v>70</v>
       </c>
       <c r="C75">
-        <f>C74 + $K$2</f>
+        <f t="shared" si="16"/>
         <v>4.499999999999992</v>
       </c>
       <c r="D75">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>9.663568597879868</v>
       </c>
       <c r="E75">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>5.3999333830329785</v>
       </c>
       <c r="F75">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.26999666915164894</v>
       </c>
       <c r="G75">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>4.5249999999999924</v>
       </c>
       <c r="H75">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>9.7985669324556923</v>
       </c>
       <c r="I75">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>5.3716288114629016</v>
       </c>
       <c r="J75">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0.26858144057314509</v>
       </c>
       <c r="K75">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>9.7978593181664397</v>
       </c>
       <c r="L75">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>5.3720051803707083</v>
       </c>
       <c r="M75">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.2686002590185354</v>
       </c>
       <c r="N75">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>4.5499999999999918</v>
       </c>
       <c r="O75">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>9.9321688568984037</v>
       </c>
       <c r="P75">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>5.3339583404903497</v>
       </c>
       <c r="Q75">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.26669791702451751</v>
       </c>
     </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B76">
         <v>71</v>
       </c>
       <c r="C76">
-        <f>C75 + $K$2</f>
+        <f t="shared" si="16"/>
         <v>4.5499999999999918</v>
       </c>
       <c r="D76">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>9.9320782621064563</v>
       </c>
       <c r="E76">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>5.3340145797370671</v>
       </c>
       <c r="F76">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.26670072898685337</v>
       </c>
       <c r="G76">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>4.5749999999999922</v>
       </c>
       <c r="H76">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10.065428626599884</v>
       </c>
       <c r="I76">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>5.2872908475851395</v>
       </c>
       <c r="J76">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0.26436454237925699</v>
       </c>
       <c r="K76">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10.064260533296085</v>
       </c>
       <c r="L76">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>5.2881102279578593</v>
       </c>
       <c r="M76">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.26440551139789298</v>
       </c>
       <c r="N76">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>4.5999999999999917</v>
       </c>
       <c r="O76">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>10.196483773504349</v>
       </c>
       <c r="P76">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>5.2339897951053453</v>
       </c>
       <c r="Q76">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.2616994897552673</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B77">
         <v>72</v>
       </c>
       <c r="C77">
-        <f>C76 + $K$2</f>
+        <f t="shared" si="16"/>
         <v>4.5999999999999917</v>
       </c>
       <c r="D77">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>10.196401649822526</v>
       </c>
       <c r="E77">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>5.2340533026114358</v>
       </c>
       <c r="F77">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.26170266513057178</v>
       </c>
       <c r="G77">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>4.624999999999992</v>
       </c>
       <c r="H77">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10.327252982387812</v>
       </c>
       <c r="I77">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>5.1738035533655156</v>
       </c>
       <c r="J77">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0.25869017766827579</v>
       </c>
       <c r="K77">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10.325746738656663</v>
       </c>
       <c r="L77">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>5.1750620768156512</v>
       </c>
       <c r="M77">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.25875310384078259</v>
       </c>
       <c r="N77">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>4.6499999999999915</v>
       </c>
       <c r="O77">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>10.455154753663308</v>
       </c>
       <c r="P77">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>5.1100313920833562</v>
       </c>
       <c r="Q77">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.25550156960416781</v>
       </c>
     </row>
-    <row r="78" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B78">
         <v>73</v>
       </c>
       <c r="C78">
-        <f>C77 + $K$2</f>
+        <f t="shared" si="16"/>
         <v>4.6499999999999915</v>
       </c>
       <c r="D78">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>10.455083449448002</v>
       </c>
       <c r="E78">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>5.1100947021156591</v>
       </c>
       <c r="F78">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.25550473510578298</v>
       </c>
       <c r="G78">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>4.6749999999999918</v>
       </c>
       <c r="H78">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10.582835817000895</v>
       </c>
       <c r="I78">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>5.0415977099855844</v>
       </c>
       <c r="J78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0.25207988549927923</v>
       </c>
       <c r="K78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10.581123392197641</v>
       </c>
       <c r="L78">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>5.0431903767306192</v>
       </c>
       <c r="M78">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.25215951883653098</v>
       </c>
       <c r="N78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>4.6999999999999913</v>
       </c>
       <c r="O78">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>10.707242968284534</v>
       </c>
       <c r="P78">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>4.9724537469519898</v>
       </c>
       <c r="Q78">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.24862268734759951</v>
       </c>
     </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B79">
         <v>74</v>
       </c>
       <c r="C79">
-        <f>C78 + $K$2</f>
+        <f t="shared" si="16"/>
         <v>4.6999999999999913</v>
       </c>
       <c r="D79">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>10.707184487968837</v>
       </c>
       <c r="E79">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>4.9725100144259908</v>
       </c>
       <c r="F79">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.24862550072129955</v>
       </c>
       <c r="G79">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>4.7249999999999917</v>
       </c>
       <c r="H79">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>10.831497238329487</v>
       </c>
       <c r="I79">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>4.9007701749331387</v>
       </c>
       <c r="J79">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0.24503850874665695</v>
       </c>
       <c r="K79">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>10.829703742342165</v>
       </c>
       <c r="L79">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>4.9025354647529538</v>
       </c>
       <c r="M79">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.2451267732376477</v>
       </c>
       <c r="N79">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>4.7499999999999911</v>
       </c>
       <c r="O79">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>10.952311261206484</v>
       </c>
       <c r="P79">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>4.8307859138499305</v>
       </c>
       <c r="Q79">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.24153929569249655</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B80">
         <v>75</v>
       </c>
       <c r="C80">
-        <f>C79 + $K$2</f>
+        <f t="shared" si="16"/>
         <v>4.7499999999999911</v>
       </c>
       <c r="D80">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>10.952267048032571</v>
       </c>
       <c r="E80">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>4.8308299824330678</v>
       </c>
       <c r="F80">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.2415414991216534</v>
       </c>
       <c r="G80">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>4.7749999999999915</v>
       </c>
       <c r="H80">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>11.073037797593397</v>
       </c>
       <c r="I80">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>4.7601480556479796</v>
       </c>
       <c r="J80">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0.23800740278239899</v>
       </c>
       <c r="K80">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>11.071270749423769</v>
       </c>
       <c r="L80">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>4.7619149311866957</v>
       </c>
       <c r="M80">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.2380957465593348</v>
       </c>
       <c r="N80">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>4.7999999999999909</v>
       </c>
       <c r="O80">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>11.190362794591906</v>
       </c>
       <c r="P80">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>4.6930275863142867</v>
       </c>
       <c r="Q80">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.23465137931571434</v>
       </c>
     </row>
-    <row r="81" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B81">
         <v>76</v>
       </c>
       <c r="C81">
-        <f>C80 + $K$2</f>
+        <f t="shared" si="16"/>
         <v>4.7999999999999909</v>
       </c>
       <c r="D81">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>11.19033357755271</v>
       </c>
       <c r="E81">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>4.6930566357514421</v>
       </c>
       <c r="F81">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.23465283178757212</v>
       </c>
       <c r="G81">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>4.8249999999999913</v>
       </c>
       <c r="H81">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>11.307659993446496</v>
       </c>
       <c r="I81">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>4.6268455390257746</v>
       </c>
       <c r="J81">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0.23134227695128873</v>
       </c>
       <c r="K81">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>11.306004716028355</v>
       </c>
       <c r="L81">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>4.6284682643524562</v>
       </c>
       <c r="M81">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.23142341321762283</v>
       </c>
       <c r="N81">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>4.8499999999999908</v>
       </c>
       <c r="O81">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>11.421756990770334</v>
       </c>
       <c r="P81">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>4.5654167415650058</v>
       </c>
       <c r="Q81">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.2282708370782503</v>
       </c>
     </row>
-    <row r="82" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B82">
         <v>77</v>
       </c>
       <c r="C82">
-        <f>C81 + $K$2</f>
+        <f t="shared" si="16"/>
         <v>4.8499999999999908</v>
       </c>
       <c r="D82">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>11.421742752419984</v>
       </c>
       <c r="E82">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>4.5654303912073262</v>
       </c>
       <c r="F82">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.22827151956036631</v>
       </c>
       <c r="G82">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>4.8749999999999911</v>
       </c>
       <c r="H82">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>11.535878512200167</v>
       </c>
       <c r="I82">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>4.5062227544956759</v>
       </c>
       <c r="J82">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0.22531113772478381</v>
       </c>
       <c r="K82">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>11.534398321282376</v>
       </c>
       <c r="L82">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>4.5075990217898578</v>
       </c>
       <c r="M82">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.22537995108949291</v>
       </c>
       <c r="N82">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>4.8999999999999906</v>
       </c>
       <c r="O82">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>11.647122703509478</v>
       </c>
       <c r="P82">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>4.4525272296146712</v>
       </c>
       <c r="Q82">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.22262636148073356</v>
       </c>
     </row>
-    <row r="83" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B83">
         <v>78</v>
       </c>
       <c r="C83">
-        <f>C82 + $K$2</f>
+        <f t="shared" si="16"/>
         <v>4.8999999999999906</v>
       </c>
       <c r="D83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>11.64712276219826</v>
       </c>
       <c r="E83">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>4.4525271771294372</v>
       </c>
       <c r="F83">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.22262635885647186</v>
       </c>
       <c r="G83">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>4.9249999999999909</v>
       </c>
       <c r="H83">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>11.758435941626496</v>
       </c>
       <c r="I83">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>4.4020991154764832</v>
       </c>
       <c r="J83">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0.22010495577382416</v>
       </c>
       <c r="K83">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>11.757175240085171</v>
       </c>
       <c r="L83">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>4.4031741445218362</v>
       </c>
       <c r="M83">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.22015870722609182</v>
       </c>
       <c r="N83">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>4.9499999999999904</v>
       </c>
       <c r="O83">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>11.867281469424352</v>
       </c>
       <c r="P83">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>4.3575503820301087</v>
       </c>
       <c r="Q83">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.21787751910150543</v>
       </c>
     </row>
-    <row r="84" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B84">
         <v>79</v>
       </c>
       <c r="C84">
-        <f>C83 + $K$2</f>
+        <f t="shared" si="16"/>
         <v>4.9499999999999904</v>
       </c>
       <c r="D84">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>11.867294629524562</v>
       </c>
       <c r="E84">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>4.3575397802059319</v>
       </c>
       <c r="F84">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.21787698901029662</v>
       </c>
       <c r="G84">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>4.9749999999999908</v>
       </c>
       <c r="H84">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>11.97623312402971</v>
       </c>
       <c r="I84">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>4.3170842460360799</v>
       </c>
       <c r="J84">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0.21585421230180402</v>
       </c>
       <c r="K84">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>11.975221735675463</v>
       </c>
       <c r="L84">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>4.3178462504078992</v>
       </c>
       <c r="M84">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.21589231252039498</v>
       </c>
       <c r="N84">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>4.9999999999999902</v>
       </c>
       <c r="O84">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>12.083186942044957</v>
       </c>
       <c r="P84">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>4.2826427700797467</v>
       </c>
       <c r="Q84">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.21413213850398735</v>
       </c>
     </row>
-    <row r="85" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B85">
         <v>80</v>
       </c>
       <c r="C85">
-        <f>C84 + $K$2</f>
+        <f t="shared" si="16"/>
         <v>4.9999999999999902</v>
       </c>
       <c r="D85">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>12.083211659051008</v>
       </c>
       <c r="E85">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>4.282625549823913</v>
       </c>
       <c r="F85">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.21413127749119565</v>
       </c>
       <c r="G85">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>5.0249999999999906</v>
       </c>
       <c r="H85">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>12.190277297796605</v>
       </c>
       <c r="I85">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>4.2529298943976963</v>
       </c>
       <c r="J85">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0.21264649471988484</v>
       </c>
       <c r="K85">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>12.18953490641095</v>
       </c>
       <c r="L85">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>4.2534019245863419</v>
       </c>
       <c r="M85">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.2126700962293171</v>
       </c>
       <c r="N85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>5.0499999999999901</v>
       </c>
       <c r="O85">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>12.295881755280325</v>
       </c>
       <c r="P85">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>4.2292649447962987</v>
       </c>
       <c r="Q85">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.21146324723981494</v>
       </c>
     </row>
@@ -13719,13 +13718,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B4277E5-85D9-40FD-8A0F-DC3D00351BB2}">
+  <sheetPr codeName="Лист3"/>
   <dimension ref="A1:Q85"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="14.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="I1" t="s">
         <v>2</v>
       </c>
@@ -13739,7 +13739,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="I2" t="s">
         <v>0</v>
       </c>
@@ -13753,7 +13753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
@@ -13806,7 +13806,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5">
         <v>0</v>
@@ -13872,7 +13872,7 @@
         <v>1.154820699103269E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6">
         <v>1</v>
@@ -13938,7 +13938,7 @@
         <v>1.5127104817839177E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="B7">
         <v>2</v>
@@ -14004,7 +14004,7 @@
         <v>1.8647580070853893E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8">
         <v>3</v>
@@ -14070,7 +14070,7 @@
         <v>2.2096739297550783E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -14090,7 +14090,7 @@
         <v>0.44192836466837937</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="B10">
         <v>5</v>
@@ -14108,7 +14108,7 @@
         <v>0.50928254418879948</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>6</v>
       </c>
@@ -14125,7 +14125,7 @@
         <v>0.57485298415147468</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B12">
         <v>7</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>0.63852870161035025</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B13">
         <v>8</v>
       </c>
@@ -14159,7 +14159,7 @@
         <v>0.70023641451034602</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B14">
         <v>9</v>
       </c>
@@ -14176,7 +14176,7 @@
         <v>0.75993515637352638</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B15">
         <v>10</v>
       </c>
@@ -14193,7 +14193,7 @@
         <v>0.8176114359056833</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B16">
         <v>11</v>
       </c>
@@ -14210,7 +14210,7 @@
         <v>0.87327488723428204</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17">
         <v>12</v>
       </c>
@@ -14227,7 +14227,7 @@
         <v>0.92695446794092262</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18">
         <v>13</v>
       </c>
@@ -14244,7 +14244,7 @@
         <v>0.97869518385068321</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19">
         <v>14</v>
       </c>
@@ -14261,7 +14261,7 @@
         <v>1.0285553141763777</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B20">
         <v>15</v>
       </c>
@@ -14278,7 +14278,7 @@
         <v>1.0766040939075014</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B21">
         <v>16</v>
       </c>
@@ -14295,7 +14295,7 @@
         <v>1.1229198064094188</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B22">
         <v>17</v>
       </c>
@@ -14312,7 +14312,7 @@
         <v>1.1675882377034426</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23">
         <v>18</v>
       </c>
@@ -14329,7 +14329,7 @@
         <v>1.2107014460920236</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24">
         <v>19</v>
       </c>
@@ -14346,7 +14346,7 @@
         <v>1.2523568046696334</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B25">
         <v>20</v>
       </c>
@@ -14363,7 +14363,7 @@
         <v>1.2926562792768066</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B26">
         <v>21</v>
       </c>
@@ -14380,7 +14380,7 @@
         <v>1.3317059099337347</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B27">
         <v>22</v>
       </c>
@@ -14397,7 +14397,7 @@
         <v>1.3696154693647542</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B28">
         <v>23</v>
       </c>
@@ -14414,7 +14414,7 @@
         <v>1.4064982776362822</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B29">
         <v>24</v>
       </c>
@@ -14431,7 +14431,7 @@
         <v>1.4424711570394222</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B30">
         <v>25</v>
       </c>
@@ -14448,7 +14448,7 @@
         <v>1.4776545160899976</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B31">
         <v>26</v>
       </c>
@@ -14465,7 +14465,7 @@
         <v>1.5121725558850549</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B32">
         <v>27</v>
       </c>
@@ -14482,7 +14482,7 @@
         <v>1.5461535960749613</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B33">
         <v>28</v>
       </c>
@@ -14499,7 +14499,7 @@
         <v>1.5797305214376214</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B34">
         <v>29</v>
       </c>
@@ -14516,7 +14516,7 @@
         <v>1.6130413535440364</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B35">
         <v>30</v>
       </c>
@@ -14533,7 +14533,7 @@
         <v>1.6462299553572066</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B36">
         <v>31</v>
       </c>
@@ -14550,7 +14550,7 @@
         <v>1.6794468798843636</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B37">
         <v>32</v>
       </c>
@@ -14567,7 +14567,7 @@
         <v>1.7128503772750077</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B38">
         <v>33</v>
       </c>
@@ -14584,7 +14584,7 @@
         <v>1.746607578080646</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B39">
         <v>34</v>
       </c>
@@ -14601,7 +14601,7 @@
         <v>1.7808958738009428</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B40">
         <v>35</v>
       </c>
@@ -14618,7 +14618,7 @@
         <v>1.8159045193346088</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B41">
         <v>36</v>
       </c>
@@ -14635,7 +14635,7 @@
         <v>1.8518364854770679</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B42">
         <v>37</v>
       </c>
@@ -14652,7 +14652,7 @@
         <v>1.8889105930229704</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B43">
         <v>38</v>
       </c>
@@ -14669,7 +14669,7 @@
         <v>1.9273639630760138</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B44">
         <v>39</v>
       </c>
@@ -14686,7 +14686,7 @@
         <v>1.9674548203861586</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B45">
         <v>40</v>
       </c>
@@ -14703,7 +14703,7 @@
         <v>2.0094656871823653</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B46">
         <v>41</v>
       </c>
@@ -14720,7 +14720,7 @@
         <v>2.0537070028734892</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B47">
         <v>42</v>
       </c>
@@ -14737,7 +14737,7 @@
         <v>2.100521198335163</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B48">
         <v>43</v>
       </c>
@@ -14754,7 +14754,7 @@
         <v>2.1502872395208863</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B49">
         <v>44</v>
       </c>
@@ -14771,7 +14771,7 @@
         <v>2.2034256296716306</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B50">
         <v>45</v>
       </c>
@@ -14788,7 +14788,7 @@
         <v>2.260403816263675</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B51">
         <v>46</v>
       </c>
@@ -14805,7 +14805,7 @@
         <v>2.3217418789322299</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B52">
         <v>47</v>
       </c>
@@ -14822,7 +14822,7 @@
         <v>2.3880182647317962</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B53">
         <v>48</v>
       </c>
@@ -14839,7 +14839,7 @@
         <v>2.4598751683675522</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B54">
         <v>49</v>
       </c>
@@ -14856,7 +14856,7 @@
         <v>2.5380229010290178</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B55">
         <v>50</v>
       </c>
@@ -14873,7 +14873,7 @@
         <v>2.6232422162331002</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B56">
         <v>51</v>
       </c>
@@ -14890,7 +14890,7 @@
         <v>2.7163830178061663</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B57">
         <v>52</v>
       </c>
@@ -14907,7 +14907,7 @@
         <v>2.8183571069021474</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B58">
         <v>53</v>
       </c>
@@ -14924,7 +14924,7 @@
         <v>2.9301215710838244</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B59">
         <v>54</v>
       </c>
@@ -14941,7 +14941,7 @@
         <v>3.052648032523857</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B60">
         <v>55</v>
       </c>
@@ -14958,7 +14958,7 @@
         <v>3.186871262630607</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B61">
         <v>56</v>
       </c>
@@ -14975,7 +14975,7 @@
         <v>3.3336087800190137</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B62">
         <v>57</v>
       </c>
@@ -14992,7 +14992,7 @@
         <v>3.4934413970730835</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B63">
         <v>58</v>
       </c>
@@ -15009,7 +15009,7 @@
         <v>3.6665441827797531</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B64">
         <v>59</v>
       </c>
@@ -15026,7 +15026,7 @@
         <v>3.85245965809679</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B65">
         <v>60</v>
       </c>
@@ -15043,7 +15043,7 @@
         <v>4.0498129234317268</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B66">
         <v>61</v>
       </c>
@@ -15060,7 +15060,7 @@
         <v>4.2559853382449857</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B67">
         <v>62</v>
       </c>
@@ -15077,7 +15077,7 @@
         <v>4.466792386144645</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B68">
         <v>63</v>
       </c>
@@ -15094,7 +15094,7 @@
         <v>4.6762518452515396</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B69">
         <v>64</v>
       </c>
@@ -15111,7 +15111,7 @@
         <v>4.8765705852033188</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B70">
         <v>65</v>
       </c>
@@ -15128,7 +15128,7 @@
         <v>5.058498029215448</v>
       </c>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B71">
         <v>66</v>
       </c>
@@ -15145,7 +15145,7 @@
         <v>5.2121550608272971</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B72">
         <v>67</v>
       </c>
@@ -15162,7 +15162,7 @@
         <v>5.3283198438906778</v>
       </c>
     </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B73">
         <v>68</v>
       </c>
@@ -15179,7 +15179,7 @@
         <v>5.3999524040896194</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B74">
         <v>69</v>
       </c>
@@ -15196,7 +15196,7 @@
         <v>5.4235556318205109</v>
       </c>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B75">
         <v>70</v>
       </c>
@@ -15213,7 +15213,7 @@
         <v>5.3999301515146829</v>
       </c>
     </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B76">
         <v>71</v>
       </c>
@@ -15230,7 +15230,7 @@
         <v>5.3340551138801153</v>
       </c>
     </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B77">
         <v>72</v>
       </c>
@@ -15247,7 +15247,7 @@
         <v>5.2341458222582062</v>
       </c>
     </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B78">
         <v>73</v>
       </c>
@@ -15264,7 +15264,7 @@
         <v>5.1102251260952158</v>
       </c>
     </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B79">
         <v>74</v>
       </c>
@@ -15281,7 +15281,7 @@
         <v>4.9726514573550986</v>
       </c>
     </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B80">
         <v>75</v>
       </c>
@@ -15298,7 +15298,7 @@
         <v>4.8309561226897699</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B81">
         <v>76</v>
       </c>
@@ -15315,7 +15315,7 @@
         <v>4.6931509102599414</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B82">
         <v>77</v>
       </c>
@@ -15332,7 +15332,7 @@
         <v>4.5654882103599483</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B83">
         <v>78</v>
       </c>
@@ -15349,7 +15349,7 @@
         <v>4.4525530621474818</v>
       </c>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B84">
         <v>79</v>
       </c>
@@ -15366,7 +15366,7 @@
         <v>4.3575427961843536</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B85">
         <v>80</v>
       </c>
@@ -15395,8 +15395,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1AF9638-C84A-4308-A33D-EDF943B0B5C5}">
+  <sheetPr codeName="Лист4"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
